--- a/data/nzd0154/nzd0154.xlsx
+++ b/data/nzd0154/nzd0154.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W341"/>
+  <dimension ref="A1:W344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25991,6 +25991,231 @@
       <c r="W341" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>272.59</v>
+      </c>
+      <c r="C342" t="n">
+        <v>280.99</v>
+      </c>
+      <c r="D342" t="n">
+        <v>279.84</v>
+      </c>
+      <c r="E342" t="n">
+        <v>289.74</v>
+      </c>
+      <c r="F342" t="n">
+        <v>300.9</v>
+      </c>
+      <c r="G342" t="n">
+        <v>292.26</v>
+      </c>
+      <c r="H342" t="n">
+        <v>290.45</v>
+      </c>
+      <c r="I342" t="n">
+        <v>291.96</v>
+      </c>
+      <c r="J342" t="n">
+        <v>301.94</v>
+      </c>
+      <c r="K342" t="n">
+        <v>313.53</v>
+      </c>
+      <c r="L342" t="n">
+        <v>316.3</v>
+      </c>
+      <c r="M342" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="N342" t="n">
+        <v>322.11</v>
+      </c>
+      <c r="O342" t="n">
+        <v>325.23</v>
+      </c>
+      <c r="P342" t="n">
+        <v>326.28</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>328.74</v>
+      </c>
+      <c r="R342" t="n">
+        <v>325.36</v>
+      </c>
+      <c r="S342" t="n">
+        <v>326.79</v>
+      </c>
+      <c r="T342" t="n">
+        <v>327.71</v>
+      </c>
+      <c r="U342" t="n">
+        <v>327.09</v>
+      </c>
+      <c r="V342" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>273.3</v>
+      </c>
+      <c r="C343" t="n">
+        <v>279.91</v>
+      </c>
+      <c r="D343" t="n">
+        <v>281</v>
+      </c>
+      <c r="E343" t="n">
+        <v>290.76</v>
+      </c>
+      <c r="F343" t="n">
+        <v>300.23</v>
+      </c>
+      <c r="G343" t="n">
+        <v>291.45</v>
+      </c>
+      <c r="H343" t="n">
+        <v>289.95</v>
+      </c>
+      <c r="I343" t="n">
+        <v>291.49</v>
+      </c>
+      <c r="J343" t="n">
+        <v>302.41</v>
+      </c>
+      <c r="K343" t="n">
+        <v>312.81</v>
+      </c>
+      <c r="L343" t="n">
+        <v>316.55</v>
+      </c>
+      <c r="M343" t="n">
+        <v>317.06</v>
+      </c>
+      <c r="N343" t="n">
+        <v>322.32</v>
+      </c>
+      <c r="O343" t="n">
+        <v>324.12</v>
+      </c>
+      <c r="P343" t="n">
+        <v>326.58</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>327.81</v>
+      </c>
+      <c r="R343" t="n">
+        <v>325</v>
+      </c>
+      <c r="S343" t="n">
+        <v>327.72</v>
+      </c>
+      <c r="T343" t="n">
+        <v>324.44</v>
+      </c>
+      <c r="U343" t="n">
+        <v>323.61</v>
+      </c>
+      <c r="V343" t="n">
+        <v>327.63</v>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>278.76</v>
+      </c>
+      <c r="C344" t="n">
+        <v>282.11</v>
+      </c>
+      <c r="D344" t="n">
+        <v>283.11</v>
+      </c>
+      <c r="E344" t="n">
+        <v>291.27</v>
+      </c>
+      <c r="F344" t="n">
+        <v>299.71</v>
+      </c>
+      <c r="G344" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="H344" t="n">
+        <v>290.86</v>
+      </c>
+      <c r="I344" t="n">
+        <v>293.15</v>
+      </c>
+      <c r="J344" t="n">
+        <v>304.48</v>
+      </c>
+      <c r="K344" t="n">
+        <v>314.68</v>
+      </c>
+      <c r="L344" t="n">
+        <v>318.31</v>
+      </c>
+      <c r="M344" t="n">
+        <v>319.19</v>
+      </c>
+      <c r="N344" t="n">
+        <v>324.43</v>
+      </c>
+      <c r="O344" t="n">
+        <v>326.63</v>
+      </c>
+      <c r="P344" t="n">
+        <v>329.2</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>330.83</v>
+      </c>
+      <c r="R344" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="S344" t="n">
+        <v>330.99</v>
+      </c>
+      <c r="T344" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="U344" t="n">
+        <v>327.83</v>
+      </c>
+      <c r="V344" t="n">
+        <v>329.85</v>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26005,7 +26230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B344"/>
+  <dimension ref="A1:B347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29448,6 +29673,36 @@
       </c>
       <c r="B344" t="n">
         <v>-0.44</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -29616,28 +29871,28 @@
         <v>0.035</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4466194223389842</v>
+        <v>0.4149172166327194</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03393448874899241</v>
+        <v>0.02968279347712421</v>
       </c>
       <c r="M2" t="n">
-        <v>14.71270213976457</v>
+        <v>14.76921416169972</v>
       </c>
       <c r="N2" t="n">
-        <v>310.0238876300959</v>
+        <v>310.2972860485419</v>
       </c>
       <c r="O2" t="n">
-        <v>17.60749521170163</v>
+        <v>17.61525719507217</v>
       </c>
       <c r="P2" t="n">
-        <v>281.580282943668</v>
+        <v>281.915922361351</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29694,28 +29949,28 @@
         <v>0.0704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3760523502995249</v>
+        <v>0.3561694937324902</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05267805389578095</v>
+        <v>0.0479859347759154</v>
       </c>
       <c r="M3" t="n">
-        <v>9.175158799525251</v>
+        <v>9.192268545270254</v>
       </c>
       <c r="N3" t="n">
-        <v>137.6233229664761</v>
+        <v>137.5593376687697</v>
       </c>
       <c r="O3" t="n">
-        <v>11.73129672996451</v>
+        <v>11.72856929334391</v>
       </c>
       <c r="P3" t="n">
-        <v>282.592563318466</v>
+        <v>282.8042709210008</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29772,28 +30027,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3330971571041159</v>
+        <v>0.3133295251750939</v>
       </c>
       <c r="J4" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0856703391093091</v>
+        <v>0.07662099218517349</v>
       </c>
       <c r="M4" t="n">
-        <v>6.634631358025338</v>
+        <v>6.670631031900085</v>
       </c>
       <c r="N4" t="n">
-        <v>64.5014467078169</v>
+        <v>65.08831785988551</v>
       </c>
       <c r="O4" t="n">
-        <v>8.03127926969402</v>
+        <v>8.067733130185053</v>
       </c>
       <c r="P4" t="n">
-        <v>284.0443774558852</v>
+        <v>284.2537864827841</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29850,28 +30105,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3052774249522784</v>
+        <v>0.2822343784485101</v>
       </c>
       <c r="J5" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1013815549793672</v>
+        <v>0.0867239465154136</v>
       </c>
       <c r="M5" t="n">
-        <v>5.569310714275207</v>
+        <v>5.633319860667102</v>
       </c>
       <c r="N5" t="n">
-        <v>44.99466687346378</v>
+        <v>46.14780460140702</v>
       </c>
       <c r="O5" t="n">
-        <v>6.707806412938866</v>
+        <v>6.793217544095508</v>
       </c>
       <c r="P5" t="n">
-        <v>295.9666427108986</v>
+        <v>296.2107634874185</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29928,28 +30183,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2360202369838595</v>
+        <v>0.2174199929852145</v>
       </c>
       <c r="J6" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K6" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08688553806859822</v>
+        <v>0.07384352461214438</v>
       </c>
       <c r="M6" t="n">
-        <v>4.621658272303605</v>
+        <v>4.674323918064981</v>
       </c>
       <c r="N6" t="n">
-        <v>31.88830910803658</v>
+        <v>32.61662989623483</v>
       </c>
       <c r="O6" t="n">
-        <v>5.646973446726714</v>
+        <v>5.711097083418809</v>
       </c>
       <c r="P6" t="n">
-        <v>304.8943432518524</v>
+        <v>305.0914109422678</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30006,28 +30261,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1788292361398031</v>
+        <v>0.1594754279318489</v>
       </c>
       <c r="J7" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K7" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05315898173760758</v>
+        <v>0.04207686015154632</v>
       </c>
       <c r="M7" t="n">
-        <v>4.473500285111147</v>
+        <v>4.532419036090572</v>
       </c>
       <c r="N7" t="n">
-        <v>31.34279712261092</v>
+        <v>32.17527459201361</v>
       </c>
       <c r="O7" t="n">
-        <v>5.598463818103223</v>
+        <v>5.672325324945106</v>
       </c>
       <c r="P7" t="n">
-        <v>298.3691488363144</v>
+        <v>298.5727321493502</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30084,28 +30339,28 @@
         <v>0.1817</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1727875767373274</v>
+        <v>0.1554774674776865</v>
       </c>
       <c r="J8" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K8" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05995770082880414</v>
+        <v>0.04840150023331158</v>
       </c>
       <c r="M8" t="n">
-        <v>4.010698389331603</v>
+        <v>4.069021107791265</v>
       </c>
       <c r="N8" t="n">
-        <v>25.49662719212232</v>
+        <v>26.14556447698216</v>
       </c>
       <c r="O8" t="n">
-        <v>5.049418500394111</v>
+        <v>5.113273362238925</v>
       </c>
       <c r="P8" t="n">
-        <v>295.9569684029206</v>
+        <v>296.1403581905117</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30162,28 +30417,28 @@
         <v>0.181</v>
       </c>
       <c r="I9" t="n">
-        <v>0.217061062056944</v>
+        <v>0.1949212671733326</v>
       </c>
       <c r="J9" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K9" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07569514903502206</v>
+        <v>0.06044030279865753</v>
       </c>
       <c r="M9" t="n">
-        <v>4.562859373941292</v>
+        <v>4.646596659554595</v>
       </c>
       <c r="N9" t="n">
-        <v>31.33764179021331</v>
+        <v>32.49259377670359</v>
       </c>
       <c r="O9" t="n">
-        <v>5.598003375330646</v>
+        <v>5.700227519731435</v>
       </c>
       <c r="P9" t="n">
-        <v>299.3813797495079</v>
+        <v>299.6159330580717</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30240,28 +30495,28 @@
         <v>0.1413</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1517011607644995</v>
+        <v>0.1309454740907767</v>
       </c>
       <c r="J10" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K10" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04481490597374171</v>
+        <v>0.0328786325560454</v>
       </c>
       <c r="M10" t="n">
-        <v>4.25130475398278</v>
+        <v>4.314582147571723</v>
       </c>
       <c r="N10" t="n">
-        <v>26.71764256653424</v>
+        <v>27.74702323405171</v>
       </c>
       <c r="O10" t="n">
-        <v>5.168911158700084</v>
+        <v>5.2675443267287</v>
       </c>
       <c r="P10" t="n">
-        <v>311.0493753587226</v>
+        <v>311.2692566262594</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30318,28 +30573,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09500402509319568</v>
+        <v>0.08050935968789888</v>
       </c>
       <c r="J11" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K11" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L11" t="n">
-        <v>0.019534521885052</v>
+        <v>0.01402366728699045</v>
       </c>
       <c r="M11" t="n">
-        <v>4.026020853779511</v>
+        <v>4.072417530885614</v>
       </c>
       <c r="N11" t="n">
-        <v>24.42789058443214</v>
+        <v>24.82039126007672</v>
       </c>
       <c r="O11" t="n">
-        <v>4.942457949687801</v>
+        <v>4.982006750304211</v>
       </c>
       <c r="P11" t="n">
-        <v>319.5500610531994</v>
+        <v>319.7047066345562</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30396,28 +30651,28 @@
         <v>0.1257</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1747705914401986</v>
+        <v>0.1607017041395699</v>
       </c>
       <c r="J12" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K12" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08208020169224162</v>
+        <v>0.06949880490349614</v>
       </c>
       <c r="M12" t="n">
-        <v>3.370819602846469</v>
+        <v>3.422619736318917</v>
       </c>
       <c r="N12" t="n">
-        <v>18.41939952263314</v>
+        <v>18.83178773950142</v>
       </c>
       <c r="O12" t="n">
-        <v>4.291782790709839</v>
+        <v>4.339560777256313</v>
       </c>
       <c r="P12" t="n">
-        <v>320.5733002001052</v>
+        <v>320.7233977124287</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30474,28 +30729,28 @@
         <v>0.1818</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1207260383920788</v>
+        <v>0.1037083560500218</v>
       </c>
       <c r="J13" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K13" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03207637599801005</v>
+        <v>0.02348551234795249</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6260427337084</v>
+        <v>3.678556552142577</v>
       </c>
       <c r="N13" t="n">
-        <v>24.20014629907633</v>
+        <v>24.85155233314191</v>
       </c>
       <c r="O13" t="n">
-        <v>4.919364420235232</v>
+        <v>4.98513313093461</v>
       </c>
       <c r="P13" t="n">
-        <v>324.6421983775592</v>
+        <v>324.8211916763109</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30552,28 +30807,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1532182664290415</v>
+        <v>0.1374594631803548</v>
       </c>
       <c r="J14" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K14" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04453609472180009</v>
+        <v>0.03588175608818578</v>
       </c>
       <c r="M14" t="n">
-        <v>4.150499567286603</v>
+        <v>4.200957894881827</v>
       </c>
       <c r="N14" t="n">
-        <v>27.71299988869522</v>
+        <v>28.21325981085256</v>
       </c>
       <c r="O14" t="n">
-        <v>5.264313809861188</v>
+        <v>5.311615555633951</v>
       </c>
       <c r="P14" t="n">
-        <v>328.1777808401185</v>
+        <v>328.3435303141193</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30630,28 +30885,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1353219106587708</v>
+        <v>0.125068185040002</v>
       </c>
       <c r="J15" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K15" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02864584377552937</v>
+        <v>0.02479485886233768</v>
       </c>
       <c r="M15" t="n">
-        <v>4.814422862899564</v>
+        <v>4.824090609770007</v>
       </c>
       <c r="N15" t="n">
-        <v>34.16744658267969</v>
+        <v>34.18813470388137</v>
       </c>
       <c r="O15" t="n">
-        <v>5.845292685801088</v>
+        <v>5.847062057467952</v>
       </c>
       <c r="P15" t="n">
-        <v>327.786707352064</v>
+        <v>327.8945556715636</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30708,28 +30963,28 @@
         <v>0.1317</v>
       </c>
       <c r="I16" t="n">
-        <v>0.06691903531912252</v>
+        <v>0.06106189120235424</v>
       </c>
       <c r="J16" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K16" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00737789415515111</v>
+        <v>0.006244771801792948</v>
       </c>
       <c r="M16" t="n">
-        <v>4.706702016621643</v>
+        <v>4.696754762282735</v>
       </c>
       <c r="N16" t="n">
-        <v>32.48802417617643</v>
+        <v>32.31575769612572</v>
       </c>
       <c r="O16" t="n">
-        <v>5.699826679485652</v>
+        <v>5.684695039852685</v>
       </c>
       <c r="P16" t="n">
-        <v>328.9733932046761</v>
+        <v>329.0358691353624</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30786,28 +31041,28 @@
         <v>0.1248</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1162059579586115</v>
+        <v>0.1083057971735166</v>
       </c>
       <c r="J17" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K17" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01482953241232532</v>
+        <v>0.01309689847665396</v>
       </c>
       <c r="M17" t="n">
-        <v>5.776600400450308</v>
+        <v>5.761955159501586</v>
       </c>
       <c r="N17" t="n">
-        <v>48.37412820829466</v>
+        <v>48.14159186592455</v>
       </c>
       <c r="O17" t="n">
-        <v>6.95515119952792</v>
+        <v>6.938414218387697</v>
       </c>
       <c r="P17" t="n">
-        <v>330.6231005433763</v>
+        <v>330.7073796300775</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30864,28 +31119,28 @@
         <v>0.1538</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1234261375425392</v>
+        <v>0.1146156046796043</v>
       </c>
       <c r="J18" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K18" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01902039882444539</v>
+        <v>0.0166618776049472</v>
       </c>
       <c r="M18" t="n">
-        <v>5.356975297653341</v>
+        <v>5.353250038520133</v>
       </c>
       <c r="N18" t="n">
-        <v>42.36693715154095</v>
+        <v>42.22575501643276</v>
       </c>
       <c r="O18" t="n">
-        <v>6.508988950024493</v>
+        <v>6.498134733631856</v>
       </c>
       <c r="P18" t="n">
-        <v>327.7189530351129</v>
+        <v>327.8129463516236</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30942,28 +31197,28 @@
         <v>0.1598</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1495056117822383</v>
+        <v>0.1472306913386276</v>
       </c>
       <c r="J19" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K19" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01929574926017863</v>
+        <v>0.01905813501113784</v>
       </c>
       <c r="M19" t="n">
-        <v>6.584934899739053</v>
+        <v>6.545547723496981</v>
       </c>
       <c r="N19" t="n">
-        <v>61.8794835486781</v>
+        <v>61.38012301871003</v>
       </c>
       <c r="O19" t="n">
-        <v>7.866351349175684</v>
+        <v>7.834546765366203</v>
       </c>
       <c r="P19" t="n">
-        <v>325.8747450094825</v>
+        <v>325.8988217162119</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31020,28 +31275,28 @@
         <v>0.1221</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1043804297245428</v>
+        <v>0.09775622198397386</v>
       </c>
       <c r="J20" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K20" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01003903159694397</v>
+        <v>0.008958754957013038</v>
       </c>
       <c r="M20" t="n">
-        <v>6.54138783893705</v>
+        <v>6.516077555468171</v>
       </c>
       <c r="N20" t="n">
-        <v>58.5220717710817</v>
+        <v>58.15687611252436</v>
       </c>
       <c r="O20" t="n">
-        <v>7.649972011130609</v>
+        <v>7.626065572267548</v>
       </c>
       <c r="P20" t="n">
-        <v>327.7098446373285</v>
+        <v>327.7800251588486</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31098,28 +31353,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1824449113518968</v>
+        <v>0.1779922161700474</v>
       </c>
       <c r="J21" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K21" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02062228367921959</v>
+        <v>0.01999167526948775</v>
       </c>
       <c r="M21" t="n">
-        <v>7.758390184088698</v>
+        <v>7.712243997940968</v>
       </c>
       <c r="N21" t="n">
-        <v>86.10576944670318</v>
+        <v>85.43794188224257</v>
       </c>
       <c r="O21" t="n">
-        <v>9.27931944954495</v>
+        <v>9.243264676630361</v>
       </c>
       <c r="P21" t="n">
-        <v>323.9499888904244</v>
+        <v>323.9971586570159</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31176,28 +31431,28 @@
         <v>0.1552</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1451761933654669</v>
+        <v>0.1390554923510015</v>
       </c>
       <c r="J22" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K22" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0170835892577399</v>
+        <v>0.01595876971151478</v>
       </c>
       <c r="M22" t="n">
-        <v>6.687936642108433</v>
+        <v>6.657829016368725</v>
       </c>
       <c r="N22" t="n">
-        <v>66.46532343608095</v>
+        <v>65.99519296258075</v>
       </c>
       <c r="O22" t="n">
-        <v>8.152626781355869</v>
+        <v>8.123742546547174</v>
       </c>
       <c r="P22" t="n">
-        <v>328.2605370991058</v>
+        <v>328.3252766798424</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31235,7 +31490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W341"/>
+  <dimension ref="A1:W344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71027,6 +71282,357 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-36.706997618485694,175.60872920774386</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-36.70754216955895,175.6093218543962</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-36.70813739275914,175.6098281525365</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-36.708673974335476,175.6104343628537</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-36.70921733982172,175.61106441633856</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-36.70985147391157,175.61157466356687</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-36.710414296790816,175.6121620017658</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-36.710947128629066,175.6127660762298</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-36.71143969288904,175.61345293320835</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>-36.711901239405236,175.61420034718466</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>-36.712363474779885,175.6149176462585</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-36.712829095460876,175.61560822847753</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>-36.71326368397197,175.61634764186692</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>-36.71366950009006,175.61710690539923</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>-36.71408381194942,175.6178414682594</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>-36.71449484949529,175.61859806716018</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>-36.71489642486454,175.6193655294187</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>-36.71525017320333,175.62014908688462</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>-36.71561194451444,175.62093878780072</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>-36.71594628929874,175.62174817954548</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>-36.71626040328941,175.6225572588364</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-36.70699385090917,175.60873562736822</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-36.70754790055364,175.60931208929924</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-36.70813123721625,175.6098386410222</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-36.70866856167003,175.61044358551734</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-36.709221046665505,175.61105849997554</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-36.709856254259094,175.6115678159576</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-36.71041732024399,175.61215785474212</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-36.71094997068786,175.61276217801745</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-36.71143676291723,175.61345672971066</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-36.71190604790043,175.6141949402117</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-36.71236174278924,175.61491943439387</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-36.712830072360674,175.6156072376471</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>-36.7132621694797,175.61634905006898</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>-36.713677701163384,175.6170997986383</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>-36.71408159543593,175.6178433890005</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>-36.71450192881508,175.61859250168686</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>-36.71489924497295,175.6193635400917</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>-36.715242875953216,175.62015419972468</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>-36.715638044449335,175.62092182004363</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>-36.71597453806775,175.62173129126643</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>-36.71626422250598,175.62255498832045</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-36.706964877704294,175.60878499516227</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-36.70753622630439,175.6093319811619</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-36.70812004049376,175.6098577192117</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-36.708665855337046,175.6104481968487</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-36.709223923618694,175.611053908171</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-36.70985654934225,175.61156739326566</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-36.71041181755911,175.61216540232496</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-36.710939932777556,175.61277594617033</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-36.711423858571976,175.6134734504727</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-36.71189355916943,175.6142089833207</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-36.71234954957456,175.6149320228645</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-36.71281520952718,175.61562231242127</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>-36.7132469524375,175.61636319914373</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>-36.713659156393426,175.61711586887938</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>-36.71406223788353,175.6178601634683</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>-36.71447894005538,175.61861057451063</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>-36.71488122761322,175.61937624967837</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>-36.71521721787874,175.62017217712247</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>-36.71561226377972,175.62093858024411</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>-36.71594028237633,175.6217517707297</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>-36.71624618280193,175.62256571288316</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0154/nzd0154.xlsx
+++ b/data/nzd0154/nzd0154.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W344"/>
+  <dimension ref="A1:W346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26214,6 +26214,156 @@
         <v>329.85</v>
       </c>
       <c r="W344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:06:16+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>280.38</v>
+      </c>
+      <c r="C345" t="n">
+        <v>281.85</v>
+      </c>
+      <c r="D345" t="n">
+        <v>283.77</v>
+      </c>
+      <c r="E345" t="n">
+        <v>290.94</v>
+      </c>
+      <c r="F345" t="n">
+        <v>297.59</v>
+      </c>
+      <c r="G345" t="n">
+        <v>290</v>
+      </c>
+      <c r="H345" t="n">
+        <v>290.13</v>
+      </c>
+      <c r="I345" t="n">
+        <v>292.64</v>
+      </c>
+      <c r="J345" t="n">
+        <v>304.26</v>
+      </c>
+      <c r="K345" t="n">
+        <v>314.77</v>
+      </c>
+      <c r="L345" t="n">
+        <v>318.62</v>
+      </c>
+      <c r="M345" t="n">
+        <v>318.31</v>
+      </c>
+      <c r="N345" t="n">
+        <v>323.55</v>
+      </c>
+      <c r="O345" t="n">
+        <v>324.79</v>
+      </c>
+      <c r="P345" t="n">
+        <v>328.24</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>329.83</v>
+      </c>
+      <c r="R345" t="n">
+        <v>327.02</v>
+      </c>
+      <c r="S345" t="n">
+        <v>329.96</v>
+      </c>
+      <c r="T345" t="n">
+        <v>328.17</v>
+      </c>
+      <c r="U345" t="n">
+        <v>327.14</v>
+      </c>
+      <c r="V345" t="n">
+        <v>329.71</v>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>294.19</v>
+      </c>
+      <c r="C346" t="n">
+        <v>283.41</v>
+      </c>
+      <c r="D346" t="n">
+        <v>285.69</v>
+      </c>
+      <c r="E346" t="n">
+        <v>293.05</v>
+      </c>
+      <c r="F346" t="n">
+        <v>298.79</v>
+      </c>
+      <c r="G346" t="n">
+        <v>291.86</v>
+      </c>
+      <c r="H346" t="n">
+        <v>291</v>
+      </c>
+      <c r="I346" t="n">
+        <v>294.29</v>
+      </c>
+      <c r="J346" t="n">
+        <v>305.32</v>
+      </c>
+      <c r="K346" t="n">
+        <v>316.4</v>
+      </c>
+      <c r="L346" t="n">
+        <v>320.7</v>
+      </c>
+      <c r="M346" t="n">
+        <v>320.39</v>
+      </c>
+      <c r="N346" t="n">
+        <v>326.22</v>
+      </c>
+      <c r="O346" t="n">
+        <v>327.16</v>
+      </c>
+      <c r="P346" t="n">
+        <v>330.38</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>331.29</v>
+      </c>
+      <c r="R346" t="n">
+        <v>329.24</v>
+      </c>
+      <c r="S346" t="n">
+        <v>332.4</v>
+      </c>
+      <c r="T346" t="n">
+        <v>330.67</v>
+      </c>
+      <c r="U346" t="n">
+        <v>331.36</v>
+      </c>
+      <c r="V346" t="n">
+        <v>332.2</v>
+      </c>
+      <c r="W346" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -26230,7 +26380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B347"/>
+  <dimension ref="A1:B349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29703,6 +29853,26 @@
       </c>
       <c r="B347" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -29871,28 +30041,28 @@
         <v>0.035</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4149172166327194</v>
+        <v>0.4085326852342128</v>
       </c>
       <c r="J2" t="n">
+        <v>345</v>
+      </c>
+      <c r="K2" t="n">
         <v>343</v>
       </c>
-      <c r="K2" t="n">
-        <v>341</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02968279347712421</v>
+        <v>0.02910720388540389</v>
       </c>
       <c r="M2" t="n">
-        <v>14.76921416169972</v>
+        <v>14.72857530882303</v>
       </c>
       <c r="N2" t="n">
-        <v>310.2972860485419</v>
+        <v>308.9484042098942</v>
       </c>
       <c r="O2" t="n">
-        <v>17.61525719507217</v>
+        <v>17.57692817900483</v>
       </c>
       <c r="P2" t="n">
-        <v>281.915922361351</v>
+        <v>281.9837819923798</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29949,28 +30119,28 @@
         <v>0.0704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3561694937324902</v>
+        <v>0.3452048679112024</v>
       </c>
       <c r="J3" t="n">
+        <v>345</v>
+      </c>
+      <c r="K3" t="n">
         <v>343</v>
       </c>
-      <c r="K3" t="n">
-        <v>341</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0479859347759154</v>
+        <v>0.04557546964262826</v>
       </c>
       <c r="M3" t="n">
-        <v>9.192268545270254</v>
+        <v>9.193511871002029</v>
       </c>
       <c r="N3" t="n">
-        <v>137.5593376687697</v>
+        <v>137.2920937631145</v>
       </c>
       <c r="O3" t="n">
-        <v>11.72856929334391</v>
+        <v>11.71717089416701</v>
       </c>
       <c r="P3" t="n">
-        <v>282.8042709210008</v>
+        <v>282.921529265929</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30027,28 +30197,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3133295251750939</v>
+        <v>0.3044498713869103</v>
       </c>
       <c r="J4" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07662099218517349</v>
+        <v>0.07311337166899412</v>
       </c>
       <c r="M4" t="n">
-        <v>6.670631031900085</v>
+        <v>6.674738619210909</v>
       </c>
       <c r="N4" t="n">
-        <v>65.08831785988551</v>
+        <v>65.0667597715737</v>
       </c>
       <c r="O4" t="n">
-        <v>8.067733130185053</v>
+        <v>8.066396951029233</v>
       </c>
       <c r="P4" t="n">
-        <v>284.2537864827841</v>
+        <v>284.3482697904269</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30105,28 +30275,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2822343784485101</v>
+        <v>0.2689826858750891</v>
       </c>
       <c r="J5" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0867239465154136</v>
+        <v>0.07905899127509486</v>
       </c>
       <c r="M5" t="n">
-        <v>5.633319860667102</v>
+        <v>5.665560353994064</v>
       </c>
       <c r="N5" t="n">
-        <v>46.14780460140702</v>
+        <v>46.66883723425394</v>
       </c>
       <c r="O5" t="n">
-        <v>6.793217544095508</v>
+        <v>6.831459378072443</v>
       </c>
       <c r="P5" t="n">
-        <v>296.2107634874185</v>
+        <v>296.351769367456</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30183,28 +30353,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2174199929852145</v>
+        <v>0.2030774903921589</v>
       </c>
       <c r="J6" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K6" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07384352461214438</v>
+        <v>0.06409285304238166</v>
       </c>
       <c r="M6" t="n">
-        <v>4.674323918064981</v>
+        <v>4.719180946152179</v>
       </c>
       <c r="N6" t="n">
-        <v>32.61662989623483</v>
+        <v>33.34605948039989</v>
       </c>
       <c r="O6" t="n">
-        <v>5.711097083418809</v>
+        <v>5.774604703388786</v>
       </c>
       <c r="P6" t="n">
-        <v>305.0914109422678</v>
+        <v>305.2440269019752</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30261,28 +30431,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1594754279318489</v>
+        <v>0.1461480090491052</v>
       </c>
       <c r="J7" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K7" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04207686015154632</v>
+        <v>0.03514554415579552</v>
       </c>
       <c r="M7" t="n">
-        <v>4.532419036090572</v>
+        <v>4.575497926229532</v>
       </c>
       <c r="N7" t="n">
-        <v>32.17527459201361</v>
+        <v>32.79725321095925</v>
       </c>
       <c r="O7" t="n">
-        <v>5.672325324945106</v>
+        <v>5.72688861520453</v>
       </c>
       <c r="P7" t="n">
-        <v>298.5727321493502</v>
+        <v>298.7135360959872</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30339,28 +30509,28 @@
         <v>0.1817</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1554774674776865</v>
+        <v>0.144495019099294</v>
       </c>
       <c r="J8" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K8" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04840150023331158</v>
+        <v>0.04175468605235721</v>
       </c>
       <c r="M8" t="n">
-        <v>4.069021107791265</v>
+        <v>4.10382999192803</v>
       </c>
       <c r="N8" t="n">
-        <v>26.14556447698216</v>
+        <v>26.5323074056828</v>
       </c>
       <c r="O8" t="n">
-        <v>5.113273362238925</v>
+        <v>5.150952087302191</v>
       </c>
       <c r="P8" t="n">
-        <v>296.1403581905117</v>
+        <v>296.2572205692948</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30417,28 +30587,28 @@
         <v>0.181</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1949212671733326</v>
+        <v>0.1821042221341246</v>
       </c>
       <c r="J9" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K9" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06044030279865753</v>
+        <v>0.05265120510605203</v>
       </c>
       <c r="M9" t="n">
-        <v>4.646596659554595</v>
+        <v>4.690959940242672</v>
       </c>
       <c r="N9" t="n">
-        <v>32.49259377670359</v>
+        <v>33.03995192681829</v>
       </c>
       <c r="O9" t="n">
-        <v>5.700227519731435</v>
+        <v>5.748038963578647</v>
       </c>
       <c r="P9" t="n">
-        <v>299.6159330580717</v>
+        <v>299.7523151948903</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30495,28 +30665,28 @@
         <v>0.1413</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1309454740907767</v>
+        <v>0.1196784274620855</v>
       </c>
       <c r="J10" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K10" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0328786325560454</v>
+        <v>0.02739908138965885</v>
       </c>
       <c r="M10" t="n">
-        <v>4.314582147571723</v>
+        <v>4.34391259707118</v>
       </c>
       <c r="N10" t="n">
-        <v>27.74702323405171</v>
+        <v>28.15322858622168</v>
       </c>
       <c r="O10" t="n">
-        <v>5.2675443267287</v>
+        <v>5.305961608061415</v>
       </c>
       <c r="P10" t="n">
-        <v>311.2692566262594</v>
+        <v>311.3891468653681</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30573,28 +30743,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08050935968789888</v>
+        <v>0.07336727859039115</v>
       </c>
       <c r="J11" t="n">
+        <v>345</v>
+      </c>
+      <c r="K11" t="n">
         <v>343</v>
       </c>
-      <c r="K11" t="n">
-        <v>341</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.01402366728699045</v>
+        <v>0.01171070642159566</v>
       </c>
       <c r="M11" t="n">
-        <v>4.072417530885614</v>
+        <v>4.089818821889499</v>
       </c>
       <c r="N11" t="n">
-        <v>24.82039126007672</v>
+        <v>24.90365756142792</v>
       </c>
       <c r="O11" t="n">
-        <v>4.982006750304211</v>
+        <v>4.990356456349378</v>
       </c>
       <c r="P11" t="n">
-        <v>319.7047066345562</v>
+        <v>319.781236977435</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30651,28 +30821,28 @@
         <v>0.1257</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1607017041395699</v>
+        <v>0.154616788593981</v>
       </c>
       <c r="J12" t="n">
+        <v>345</v>
+      </c>
+      <c r="K12" t="n">
         <v>343</v>
       </c>
-      <c r="K12" t="n">
-        <v>341</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.06949880490349614</v>
+        <v>0.06487600416691741</v>
       </c>
       <c r="M12" t="n">
-        <v>3.422619736318917</v>
+        <v>3.438146061513497</v>
       </c>
       <c r="N12" t="n">
-        <v>18.83178773950142</v>
+        <v>18.89103377966197</v>
       </c>
       <c r="O12" t="n">
-        <v>4.339560777256313</v>
+        <v>4.3463816882163</v>
       </c>
       <c r="P12" t="n">
-        <v>320.7233977124287</v>
+        <v>320.7885980078685</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30729,28 +30899,28 @@
         <v>0.1818</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1037083560500218</v>
+        <v>0.0944830895806469</v>
       </c>
       <c r="J13" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K13" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02348551234795249</v>
+        <v>0.01950566216313154</v>
       </c>
       <c r="M13" t="n">
-        <v>3.678556552142577</v>
+        <v>3.70346916601631</v>
       </c>
       <c r="N13" t="n">
-        <v>24.85155233314191</v>
+        <v>25.09878483329187</v>
       </c>
       <c r="O13" t="n">
-        <v>4.98513313093461</v>
+        <v>5.00986874411814</v>
       </c>
       <c r="P13" t="n">
-        <v>324.8211916763109</v>
+        <v>324.9186541285927</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30807,28 +30977,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1374594631803548</v>
+        <v>0.1294828581512003</v>
       </c>
       <c r="J14" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K14" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03588175608818578</v>
+        <v>0.03202063354716711</v>
       </c>
       <c r="M14" t="n">
-        <v>4.200957894881827</v>
+        <v>4.220429316721706</v>
       </c>
       <c r="N14" t="n">
-        <v>28.21325981085256</v>
+        <v>28.34789823760535</v>
       </c>
       <c r="O14" t="n">
-        <v>5.311615555633951</v>
+        <v>5.324274432972566</v>
       </c>
       <c r="P14" t="n">
-        <v>328.3435303141193</v>
+        <v>328.4277984508037</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30885,28 +31055,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.125068185040002</v>
+        <v>0.119192845141264</v>
       </c>
       <c r="J15" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K15" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02479485886233768</v>
+        <v>0.02273667660327239</v>
       </c>
       <c r="M15" t="n">
-        <v>4.824090609770007</v>
+        <v>4.825820924334701</v>
       </c>
       <c r="N15" t="n">
-        <v>34.18813470388137</v>
+        <v>34.15427882423609</v>
       </c>
       <c r="O15" t="n">
-        <v>5.847062057467952</v>
+        <v>5.844166221475574</v>
       </c>
       <c r="P15" t="n">
-        <v>327.8945556715636</v>
+        <v>327.9566239918963</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30963,28 +31133,28 @@
         <v>0.1317</v>
       </c>
       <c r="I16" t="n">
-        <v>0.06106189120235424</v>
+        <v>0.05952367235560795</v>
       </c>
       <c r="J16" t="n">
+        <v>345</v>
+      </c>
+      <c r="K16" t="n">
         <v>343</v>
       </c>
-      <c r="K16" t="n">
-        <v>341</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.006244771801792948</v>
+        <v>0.006006416233448664</v>
       </c>
       <c r="M16" t="n">
-        <v>4.696754762282735</v>
+        <v>4.677551597054482</v>
       </c>
       <c r="N16" t="n">
-        <v>32.31575769612572</v>
+        <v>32.14436938731297</v>
       </c>
       <c r="O16" t="n">
-        <v>5.684695039852685</v>
+        <v>5.669600460994846</v>
       </c>
       <c r="P16" t="n">
-        <v>329.0358691353624</v>
+        <v>329.0523464803668</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31041,28 +31211,28 @@
         <v>0.1248</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1083057971735166</v>
+        <v>0.1048582122858716</v>
       </c>
       <c r="J17" t="n">
+        <v>345</v>
+      </c>
+      <c r="K17" t="n">
         <v>343</v>
       </c>
-      <c r="K17" t="n">
-        <v>341</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.01309689847665396</v>
+        <v>0.01242368384310388</v>
       </c>
       <c r="M17" t="n">
-        <v>5.761955159501586</v>
+        <v>5.743927853255166</v>
       </c>
       <c r="N17" t="n">
-        <v>48.14159186592455</v>
+        <v>47.91621363275924</v>
       </c>
       <c r="O17" t="n">
-        <v>6.938414218387697</v>
+        <v>6.922153829030329</v>
       </c>
       <c r="P17" t="n">
-        <v>330.7073796300775</v>
+        <v>330.7443199240512</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31119,28 +31289,28 @@
         <v>0.1538</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1146156046796043</v>
+        <v>0.1115039450025193</v>
       </c>
       <c r="J18" t="n">
+        <v>345</v>
+      </c>
+      <c r="K18" t="n">
         <v>343</v>
       </c>
-      <c r="K18" t="n">
-        <v>341</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.0166618776049472</v>
+        <v>0.01595874001720154</v>
       </c>
       <c r="M18" t="n">
-        <v>5.353250038520133</v>
+        <v>5.337432934971292</v>
       </c>
       <c r="N18" t="n">
-        <v>42.22575501643276</v>
+        <v>42.02933257430141</v>
       </c>
       <c r="O18" t="n">
-        <v>6.498134733631856</v>
+        <v>6.483003360657883</v>
       </c>
       <c r="P18" t="n">
-        <v>327.8129463516236</v>
+        <v>327.8462845513192</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31197,28 +31367,28 @@
         <v>0.1598</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1472306913386276</v>
+        <v>0.1487804966714077</v>
       </c>
       <c r="J19" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K19" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01905813501113784</v>
+        <v>0.01968442450171393</v>
       </c>
       <c r="M19" t="n">
-        <v>6.545547723496981</v>
+        <v>6.51534240079891</v>
       </c>
       <c r="N19" t="n">
-        <v>61.38012301871003</v>
+        <v>61.04259313331399</v>
       </c>
       <c r="O19" t="n">
-        <v>7.834546765366203</v>
+        <v>7.812975946034519</v>
       </c>
       <c r="P19" t="n">
-        <v>325.8988217162119</v>
+        <v>325.8823229366716</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31275,28 +31445,28 @@
         <v>0.1221</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09775622198397386</v>
+        <v>0.09667458762664943</v>
       </c>
       <c r="J20" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K20" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L20" t="n">
-        <v>0.008958754957013038</v>
+        <v>0.008869060830913655</v>
       </c>
       <c r="M20" t="n">
-        <v>6.516077555468171</v>
+        <v>6.485178590133879</v>
       </c>
       <c r="N20" t="n">
-        <v>58.15687611252436</v>
+        <v>57.83301602017649</v>
       </c>
       <c r="O20" t="n">
-        <v>7.626065572267548</v>
+        <v>7.604802168378642</v>
       </c>
       <c r="P20" t="n">
-        <v>327.7800251588486</v>
+        <v>327.7915275358926</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31353,28 +31523,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1779922161700474</v>
+        <v>0.1785864022746095</v>
       </c>
       <c r="J21" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K21" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01999167526948775</v>
+        <v>0.02036114475654704</v>
       </c>
       <c r="M21" t="n">
-        <v>7.712243997940968</v>
+        <v>7.679775340197252</v>
       </c>
       <c r="N21" t="n">
-        <v>85.43794188224257</v>
+        <v>84.96858238792474</v>
       </c>
       <c r="O21" t="n">
-        <v>9.243264676630361</v>
+        <v>9.217840440576348</v>
       </c>
       <c r="P21" t="n">
-        <v>323.9971586570159</v>
+        <v>323.9908234387759</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31431,28 +31601,28 @@
         <v>0.1552</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1390554923510015</v>
+        <v>0.1378515373286056</v>
       </c>
       <c r="J22" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K22" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01595876971151478</v>
+        <v>0.01587544295856824</v>
       </c>
       <c r="M22" t="n">
-        <v>6.657829016368725</v>
+        <v>6.625674659441025</v>
       </c>
       <c r="N22" t="n">
-        <v>65.99519296258075</v>
+        <v>65.62375740564168</v>
       </c>
       <c r="O22" t="n">
-        <v>8.123742546547174</v>
+        <v>8.100849178057921</v>
       </c>
       <c r="P22" t="n">
-        <v>328.3252766798424</v>
+        <v>328.3380624333245</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31490,7 +31660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W344"/>
+  <dimension ref="A1:W346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71633,6 +71803,240 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:06:16+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-36.7069562812552,175.6087996427423</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-36.70753760598855,175.6093296303057</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-36.708116538200834,175.60986368679585</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-36.7086676064937,175.61044521304612</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-36.70923565273385,175.61103518773356</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-36.709864811670414,175.61155555788952</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-36.71041623180086,175.61215934767068</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-36.710943016714005,175.61277171619605</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-36.7114252300484,175.61347167338715</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-36.711892958107484,175.61420965919217</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-36.71234740190594,175.61493424015154</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>-36.71282135004076,175.61561608434627</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>-36.713253298881824,175.61635729810848</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>-36.71367275096601,175.61710408830498</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>-36.714069330727405,175.6178540170994</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>-36.71448655222774,175.61860459013306</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>-36.71488342103099,175.61937470242464</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>-36.71522529978014,175.62016651451833</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>-36.71560827296381,175.62094117470144</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>-36.715945883425604,175.62174842219306</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>-36.71624732044094,175.62256503655954</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-36.70688299911146,175.60892450870622</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-36.707529327882924,175.60934373544148</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-36.70810634971072,175.6098810470376</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-36.70865640970299,175.61046429129667</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-36.7092290136124,175.61104578420827</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-36.70985383457705,175.61157128203155</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-36.71041097099217,175.61216656349146</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-36.71093303927205,175.61278540140577</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>-36.71141862202548,175.61348023570787</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>-36.71188207220698,175.61422189997316</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>-36.71233299174133,175.61494911742906</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>-36.712806836099126,175.61563080524922</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>-36.71323404319201,175.61637520238293</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>-36.71365524056525,175.6171192621962</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>-36.71405351959589,175.6178677183786</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>-36.71447543845603,175.6186133273239</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>-36.71486603036107,175.61938696993394</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>-36.71520615430463,175.62017992884088</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>-36.715588318883526,175.6209541469841</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>-36.71591162773169,175.62176890164173</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>-36.716227086717915,175.6225770654556</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0154/nzd0154.xlsx
+++ b/data/nzd0154/nzd0154.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W346"/>
+  <dimension ref="A1:W347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26364,6 +26364,81 @@
         <v>332.2</v>
       </c>
       <c r="W346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>294.14</v>
+      </c>
+      <c r="C347" t="n">
+        <v>285.54</v>
+      </c>
+      <c r="D347" t="n">
+        <v>287.84</v>
+      </c>
+      <c r="E347" t="n">
+        <v>295.41</v>
+      </c>
+      <c r="F347" t="n">
+        <v>300.47</v>
+      </c>
+      <c r="G347" t="n">
+        <v>293.29</v>
+      </c>
+      <c r="H347" t="n">
+        <v>292.05</v>
+      </c>
+      <c r="I347" t="n">
+        <v>296.28</v>
+      </c>
+      <c r="J347" t="n">
+        <v>305.88</v>
+      </c>
+      <c r="K347" t="n">
+        <v>316.95</v>
+      </c>
+      <c r="L347" t="n">
+        <v>320.99</v>
+      </c>
+      <c r="M347" t="n">
+        <v>322.28</v>
+      </c>
+      <c r="N347" t="n">
+        <v>327.52</v>
+      </c>
+      <c r="O347" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="P347" t="n">
+        <v>330.76</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>331.43</v>
+      </c>
+      <c r="R347" t="n">
+        <v>329.25</v>
+      </c>
+      <c r="S347" t="n">
+        <v>332.01</v>
+      </c>
+      <c r="T347" t="n">
+        <v>330.44</v>
+      </c>
+      <c r="U347" t="n">
+        <v>330.27</v>
+      </c>
+      <c r="V347" t="n">
+        <v>331.66</v>
+      </c>
+      <c r="W347" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -26380,7 +26455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B349"/>
+  <dimension ref="A1:B350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29873,6 +29948,16 @@
       </c>
       <c r="B349" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -30041,28 +30126,28 @@
         <v>0.035</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4085326852342128</v>
+        <v>0.4092491751053555</v>
       </c>
       <c r="J2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02910720388540389</v>
+        <v>0.0293813346775833</v>
       </c>
       <c r="M2" t="n">
-        <v>14.72857530882303</v>
+        <v>14.68882547009425</v>
       </c>
       <c r="N2" t="n">
-        <v>308.9484042098942</v>
+        <v>308.0549190071771</v>
       </c>
       <c r="O2" t="n">
-        <v>17.57692817900483</v>
+        <v>17.55149335547198</v>
       </c>
       <c r="P2" t="n">
-        <v>281.9837819923798</v>
+        <v>281.9761285128829</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30119,28 +30204,28 @@
         <v>0.0704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3452048679112024</v>
+        <v>0.3414550015946736</v>
       </c>
       <c r="J3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04557546964262826</v>
+        <v>0.04486014665442595</v>
       </c>
       <c r="M3" t="n">
-        <v>9.193511871002029</v>
+        <v>9.185444812611616</v>
       </c>
       <c r="N3" t="n">
-        <v>137.2920937631145</v>
+        <v>137.01802189407</v>
       </c>
       <c r="O3" t="n">
-        <v>11.71717089416701</v>
+        <v>11.70546974256352</v>
       </c>
       <c r="P3" t="n">
-        <v>282.921529265929</v>
+        <v>282.9618074931431</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30197,28 +30282,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3044498713869103</v>
+        <v>0.3018305986005643</v>
       </c>
       <c r="J4" t="n">
+        <v>346</v>
+      </c>
+      <c r="K4" t="n">
         <v>345</v>
       </c>
-      <c r="K4" t="n">
-        <v>344</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.07311337166899412</v>
+        <v>0.07230064949740511</v>
       </c>
       <c r="M4" t="n">
-        <v>6.674738619210909</v>
+        <v>6.667909822190339</v>
       </c>
       <c r="N4" t="n">
-        <v>65.0667597715737</v>
+        <v>64.93969767723861</v>
       </c>
       <c r="O4" t="n">
-        <v>8.066396951029233</v>
+        <v>8.058517089219245</v>
       </c>
       <c r="P4" t="n">
-        <v>284.3482697904269</v>
+        <v>284.3762635606916</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30275,28 +30360,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2689826858750891</v>
+        <v>0.264392367464489</v>
       </c>
       <c r="J5" t="n">
+        <v>346</v>
+      </c>
+      <c r="K5" t="n">
         <v>345</v>
       </c>
-      <c r="K5" t="n">
-        <v>344</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.07905899127509486</v>
+        <v>0.07673870330343024</v>
       </c>
       <c r="M5" t="n">
-        <v>5.665560353994064</v>
+        <v>5.671584669950004</v>
       </c>
       <c r="N5" t="n">
-        <v>46.66883723425394</v>
+        <v>46.72256530986801</v>
       </c>
       <c r="O5" t="n">
-        <v>6.831459378072443</v>
+        <v>6.835390647934323</v>
       </c>
       <c r="P5" t="n">
-        <v>296.351769367456</v>
+        <v>296.4008289078362</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30353,28 +30438,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2030774903921589</v>
+        <v>0.1973117222012385</v>
       </c>
       <c r="J6" t="n">
+        <v>346</v>
+      </c>
+      <c r="K6" t="n">
         <v>345</v>
       </c>
-      <c r="K6" t="n">
-        <v>344</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.06409285304238166</v>
+        <v>0.06056606218791749</v>
       </c>
       <c r="M6" t="n">
-        <v>4.719180946152179</v>
+        <v>4.73465043600951</v>
       </c>
       <c r="N6" t="n">
-        <v>33.34605948039989</v>
+        <v>33.54759259920504</v>
       </c>
       <c r="O6" t="n">
-        <v>5.774604703388786</v>
+        <v>5.792028366574618</v>
       </c>
       <c r="P6" t="n">
-        <v>305.2440269019752</v>
+        <v>305.3056491930851</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30431,28 +30516,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1461480090491052</v>
+        <v>0.140917325783789</v>
       </c>
       <c r="J7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03514554415579552</v>
+        <v>0.03271018963730621</v>
       </c>
       <c r="M7" t="n">
-        <v>4.575497926229532</v>
+        <v>4.589819184110389</v>
       </c>
       <c r="N7" t="n">
-        <v>32.79725321095925</v>
+        <v>32.95147651628875</v>
       </c>
       <c r="O7" t="n">
-        <v>5.72688861520453</v>
+        <v>5.740337665703016</v>
       </c>
       <c r="P7" t="n">
-        <v>298.7135360959872</v>
+        <v>298.7690441872758</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30509,28 +30594,28 @@
         <v>0.1817</v>
       </c>
       <c r="I8" t="n">
-        <v>0.144495019099294</v>
+        <v>0.139937036889438</v>
       </c>
       <c r="J8" t="n">
+        <v>346</v>
+      </c>
+      <c r="K8" t="n">
         <v>345</v>
       </c>
-      <c r="K8" t="n">
-        <v>344</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04175468605235721</v>
+        <v>0.03923194599467039</v>
       </c>
       <c r="M8" t="n">
-        <v>4.10382999192803</v>
+        <v>4.116116536471838</v>
       </c>
       <c r="N8" t="n">
-        <v>26.5323074056828</v>
+        <v>26.64174881590479</v>
       </c>
       <c r="O8" t="n">
-        <v>5.150952087302191</v>
+        <v>5.161564570544942</v>
       </c>
       <c r="P8" t="n">
-        <v>296.2572205692948</v>
+        <v>296.3059345129201</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30587,28 +30672,28 @@
         <v>0.181</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1821042221341246</v>
+        <v>0.1773899604986671</v>
       </c>
       <c r="J9" t="n">
+        <v>346</v>
+      </c>
+      <c r="K9" t="n">
         <v>345</v>
       </c>
-      <c r="K9" t="n">
-        <v>344</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.05265120510605203</v>
+        <v>0.05010199180183694</v>
       </c>
       <c r="M9" t="n">
-        <v>4.690959940242672</v>
+        <v>4.7036584800029</v>
       </c>
       <c r="N9" t="n">
-        <v>33.03995192681829</v>
+        <v>33.14352819388954</v>
       </c>
       <c r="O9" t="n">
-        <v>5.748038963578647</v>
+        <v>5.757041618217602</v>
       </c>
       <c r="P9" t="n">
-        <v>299.7523151948903</v>
+        <v>299.8026993923205</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30665,28 +30750,28 @@
         <v>0.1413</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1196784274620855</v>
+        <v>0.114756420549952</v>
       </c>
       <c r="J10" t="n">
+        <v>346</v>
+      </c>
+      <c r="K10" t="n">
         <v>345</v>
       </c>
-      <c r="K10" t="n">
-        <v>344</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02739908138965885</v>
+        <v>0.02520968495242581</v>
       </c>
       <c r="M10" t="n">
-        <v>4.34391259707118</v>
+        <v>4.354795456333021</v>
       </c>
       <c r="N10" t="n">
-        <v>28.15322858622168</v>
+        <v>28.28892554960526</v>
       </c>
       <c r="O10" t="n">
-        <v>5.305961608061415</v>
+        <v>5.318733453521173</v>
       </c>
       <c r="P10" t="n">
-        <v>311.3891468653681</v>
+        <v>311.4417513636312</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30743,28 +30828,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07336727859039115</v>
+        <v>0.07063726569145931</v>
       </c>
       <c r="J11" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K11" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01171070642159566</v>
+        <v>0.01090294023309868</v>
       </c>
       <c r="M11" t="n">
-        <v>4.089818821889499</v>
+        <v>4.093744383738148</v>
       </c>
       <c r="N11" t="n">
-        <v>24.90365756142792</v>
+        <v>24.89715226123369</v>
       </c>
       <c r="O11" t="n">
-        <v>4.990356456349378</v>
+        <v>4.989704626652132</v>
       </c>
       <c r="P11" t="n">
-        <v>319.781236977435</v>
+        <v>319.8106189144109</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30821,28 +30906,28 @@
         <v>0.1257</v>
       </c>
       <c r="I12" t="n">
-        <v>0.154616788593981</v>
+        <v>0.1523799752370807</v>
       </c>
       <c r="J12" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K12" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06487600416691741</v>
+        <v>0.06335862116086133</v>
       </c>
       <c r="M12" t="n">
-        <v>3.438146061513497</v>
+        <v>3.44117354324751</v>
       </c>
       <c r="N12" t="n">
-        <v>18.89103377966197</v>
+        <v>18.88035067500604</v>
       </c>
       <c r="O12" t="n">
-        <v>4.3463816882163</v>
+        <v>4.345152549106421</v>
       </c>
       <c r="P12" t="n">
-        <v>320.7885980078685</v>
+        <v>320.812671853492</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30899,28 +30984,28 @@
         <v>0.1818</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0944830895806469</v>
+        <v>0.09158922829311845</v>
       </c>
       <c r="J13" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K13" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01950566216313154</v>
+        <v>0.01840672699047863</v>
       </c>
       <c r="M13" t="n">
-        <v>3.70346916601631</v>
+        <v>3.707221335967861</v>
       </c>
       <c r="N13" t="n">
-        <v>25.09878483329187</v>
+        <v>25.10246354405853</v>
       </c>
       <c r="O13" t="n">
-        <v>5.00986874411814</v>
+        <v>5.010235877087877</v>
       </c>
       <c r="P13" t="n">
-        <v>324.9186541285927</v>
+        <v>324.9493638290996</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30977,28 +31062,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1294828581512003</v>
+        <v>0.1270402144106257</v>
       </c>
       <c r="J14" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K14" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03202063354716711</v>
+        <v>0.03098752849172648</v>
       </c>
       <c r="M14" t="n">
-        <v>4.220429316721706</v>
+        <v>4.221647436497892</v>
       </c>
       <c r="N14" t="n">
-        <v>28.34789823760535</v>
+        <v>28.32027110921801</v>
       </c>
       <c r="O14" t="n">
-        <v>5.324274432972566</v>
+        <v>5.321679350469926</v>
       </c>
       <c r="P14" t="n">
-        <v>328.4277984508037</v>
+        <v>328.4537198237601</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31055,28 +31140,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.119192845141264</v>
+        <v>0.1174928219965898</v>
       </c>
       <c r="J15" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K15" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02273667660327239</v>
+        <v>0.02222344632234452</v>
       </c>
       <c r="M15" t="n">
-        <v>4.825820924334701</v>
+        <v>4.820361290532832</v>
       </c>
       <c r="N15" t="n">
-        <v>34.15427882423609</v>
+        <v>34.0818706203598</v>
       </c>
       <c r="O15" t="n">
-        <v>5.844166221475574</v>
+        <v>5.837968021525966</v>
       </c>
       <c r="P15" t="n">
-        <v>327.9566239918963</v>
+        <v>327.9746646636634</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31133,28 +31218,28 @@
         <v>0.1317</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05952367235560795</v>
+        <v>0.05959084320483628</v>
       </c>
       <c r="J16" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K16" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L16" t="n">
-        <v>0.006006416233448664</v>
+        <v>0.006057117490805175</v>
       </c>
       <c r="M16" t="n">
-        <v>4.677551597054482</v>
+        <v>4.664279183392305</v>
       </c>
       <c r="N16" t="n">
-        <v>32.14436938731297</v>
+        <v>32.05096634134929</v>
       </c>
       <c r="O16" t="n">
-        <v>5.669600460994846</v>
+        <v>5.661357287908023</v>
       </c>
       <c r="P16" t="n">
-        <v>329.0523464803668</v>
+        <v>329.0516235498417</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31211,28 +31296,28 @@
         <v>0.1248</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1048582122858716</v>
+        <v>0.1036541280682289</v>
       </c>
       <c r="J17" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K17" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01242368384310388</v>
+        <v>0.01221483699880077</v>
       </c>
       <c r="M17" t="n">
-        <v>5.743927853255166</v>
+        <v>5.732753091008317</v>
       </c>
       <c r="N17" t="n">
-        <v>47.91621363275924</v>
+        <v>47.78973964496726</v>
       </c>
       <c r="O17" t="n">
-        <v>6.922153829030329</v>
+        <v>6.913012342312666</v>
       </c>
       <c r="P17" t="n">
-        <v>330.7443199240512</v>
+        <v>330.7572789568126</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31289,28 +31374,28 @@
         <v>0.1538</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1115039450025193</v>
+        <v>0.1106076599399132</v>
       </c>
       <c r="J18" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K18" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01595874001720154</v>
+        <v>0.01580077181715767</v>
       </c>
       <c r="M18" t="n">
-        <v>5.337432934971292</v>
+        <v>5.326294438219753</v>
       </c>
       <c r="N18" t="n">
-        <v>42.02933257430141</v>
+        <v>41.91425620864013</v>
       </c>
       <c r="O18" t="n">
-        <v>6.483003360657883</v>
+        <v>6.474122041531201</v>
       </c>
       <c r="P18" t="n">
-        <v>327.8462845513192</v>
+        <v>327.8559308761523</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31367,28 +31452,28 @@
         <v>0.1598</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1487804966714077</v>
+        <v>0.1500029071758751</v>
       </c>
       <c r="J19" t="n">
+        <v>346</v>
+      </c>
+      <c r="K19" t="n">
         <v>345</v>
       </c>
-      <c r="K19" t="n">
-        <v>344</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.01968442450171393</v>
+        <v>0.0201197730327427</v>
       </c>
       <c r="M19" t="n">
-        <v>6.51534240079891</v>
+        <v>6.502583737801496</v>
       </c>
       <c r="N19" t="n">
-        <v>61.04259313331399</v>
+        <v>60.8790613419981</v>
       </c>
       <c r="O19" t="n">
-        <v>7.812975946034519</v>
+        <v>7.802503530406001</v>
       </c>
       <c r="P19" t="n">
-        <v>325.8823229366716</v>
+        <v>325.8692582879608</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31445,28 +31530,28 @@
         <v>0.1221</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09667458762664943</v>
+        <v>0.09671264731669751</v>
       </c>
       <c r="J20" t="n">
+        <v>346</v>
+      </c>
+      <c r="K20" t="n">
         <v>345</v>
       </c>
-      <c r="K20" t="n">
-        <v>344</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.008869060830913655</v>
+        <v>0.00893046475662973</v>
       </c>
       <c r="M20" t="n">
-        <v>6.485178590133879</v>
+        <v>6.466583470965025</v>
       </c>
       <c r="N20" t="n">
-        <v>57.83301602017649</v>
+        <v>57.66539708260522</v>
       </c>
       <c r="O20" t="n">
-        <v>7.604802168378642</v>
+        <v>7.593773573303672</v>
       </c>
       <c r="P20" t="n">
-        <v>327.7915275358926</v>
+        <v>327.7911207687069</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31523,28 +31608,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1785864022746095</v>
+        <v>0.1794449472066879</v>
       </c>
       <c r="J21" t="n">
+        <v>346</v>
+      </c>
+      <c r="K21" t="n">
         <v>345</v>
       </c>
-      <c r="K21" t="n">
-        <v>344</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.02036114475654704</v>
+        <v>0.02067643877168834</v>
       </c>
       <c r="M21" t="n">
-        <v>7.679775340197252</v>
+        <v>7.662045882713426</v>
       </c>
       <c r="N21" t="n">
-        <v>84.96858238792474</v>
+        <v>84.72890817828319</v>
       </c>
       <c r="O21" t="n">
-        <v>9.217840440576348</v>
+        <v>9.204830697969582</v>
       </c>
       <c r="P21" t="n">
-        <v>323.9908234387759</v>
+        <v>323.9816476439843</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31601,28 +31686,28 @@
         <v>0.1552</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1378515373286056</v>
+        <v>0.1376520282747651</v>
       </c>
       <c r="J22" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K22" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01587544295856824</v>
+        <v>0.01592636532723724</v>
       </c>
       <c r="M22" t="n">
-        <v>6.625674659441025</v>
+        <v>6.607255160811632</v>
       </c>
       <c r="N22" t="n">
-        <v>65.62375740564168</v>
+        <v>65.43223530226518</v>
       </c>
       <c r="O22" t="n">
-        <v>8.100849178057921</v>
+        <v>8.089019427734438</v>
       </c>
       <c r="P22" t="n">
-        <v>328.3380624333245</v>
+        <v>328.3401918077697</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31660,7 +31745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W346"/>
+  <dimension ref="A1:W347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72037,6 +72122,123 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-36.706883264434445,175.60892405662133</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-36.70751802508233,175.6093629943719</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-36.708094940721594,175.6099004868861</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-36.70864388627492,175.61048562999676</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-36.70921971884089,175.6110606192698</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-36.70984539519752,175.61158337101938</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-36.710404621739784,175.6121752722393</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-36.71092100587043,175.6128019065934</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-36.71141513099428,175.61348475919746</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>-36.711878399050114,175.61422603029723</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>-36.71233098263171,175.61495119166446</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>-36.7127936479488,175.61564418144962</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>-36.713224667761644,175.61638391981674</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>-36.71364829551132,175.61712528053098</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>-36.71405071201165,175.61787015131543</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>-36.71447437275185,175.61861416513662</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>-36.71486595202471,175.619387025193</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>-36.7152092144422,175.62017778474876</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>-36.715590154658955,175.62095295353438</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>-36.71592047576666,175.62176361192797</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>-36.716231474754316,175.62257445677986</t>
+        </is>
+      </c>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0154/nzd0154.xlsx
+++ b/data/nzd0154/nzd0154.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W347"/>
+  <dimension ref="A1:W350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26441,6 +26441,231 @@
       <c r="W347" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>288.75</v>
+      </c>
+      <c r="C348" t="n">
+        <v>279.92</v>
+      </c>
+      <c r="D348" t="n">
+        <v>285.45</v>
+      </c>
+      <c r="E348" t="n">
+        <v>294.23</v>
+      </c>
+      <c r="F348" t="n">
+        <v>300.21</v>
+      </c>
+      <c r="G348" t="n">
+        <v>293.12</v>
+      </c>
+      <c r="H348" t="n">
+        <v>291.63</v>
+      </c>
+      <c r="I348" t="n">
+        <v>295.48</v>
+      </c>
+      <c r="J348" t="n">
+        <v>305.52</v>
+      </c>
+      <c r="K348" t="n">
+        <v>316.41</v>
+      </c>
+      <c r="L348" t="n">
+        <v>320.19</v>
+      </c>
+      <c r="M348" t="n">
+        <v>321.85</v>
+      </c>
+      <c r="N348" t="n">
+        <v>326.65</v>
+      </c>
+      <c r="O348" t="n">
+        <v>327.44</v>
+      </c>
+      <c r="P348" t="n">
+        <v>330.76</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>331.43</v>
+      </c>
+      <c r="R348" t="n">
+        <v>329.25</v>
+      </c>
+      <c r="S348" t="n">
+        <v>332.01</v>
+      </c>
+      <c r="T348" t="n">
+        <v>330.44</v>
+      </c>
+      <c r="U348" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="V348" t="n">
+        <v>328.46</v>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>285.69</v>
+      </c>
+      <c r="C349" t="n">
+        <v>275.74</v>
+      </c>
+      <c r="D349" t="n">
+        <v>284.72</v>
+      </c>
+      <c r="E349" t="n">
+        <v>294.35</v>
+      </c>
+      <c r="F349" t="n">
+        <v>299.68</v>
+      </c>
+      <c r="G349" t="n">
+        <v>293.31</v>
+      </c>
+      <c r="H349" t="n">
+        <v>292.32</v>
+      </c>
+      <c r="I349" t="n">
+        <v>296.14</v>
+      </c>
+      <c r="J349" t="n">
+        <v>306.78</v>
+      </c>
+      <c r="K349" t="n">
+        <v>316.81</v>
+      </c>
+      <c r="L349" t="n">
+        <v>321.52</v>
+      </c>
+      <c r="M349" t="n">
+        <v>323.51</v>
+      </c>
+      <c r="N349" t="n">
+        <v>327.42</v>
+      </c>
+      <c r="O349" t="n">
+        <v>327.65</v>
+      </c>
+      <c r="P349" t="n">
+        <v>331.13</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>330.71</v>
+      </c>
+      <c r="R349" t="n">
+        <v>328.22</v>
+      </c>
+      <c r="S349" t="n">
+        <v>330.19</v>
+      </c>
+      <c r="T349" t="n">
+        <v>327.01</v>
+      </c>
+      <c r="U349" t="n">
+        <v>323.68</v>
+      </c>
+      <c r="V349" t="n">
+        <v>325.87</v>
+      </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>281.39</v>
+      </c>
+      <c r="C350" t="n">
+        <v>273.42</v>
+      </c>
+      <c r="D350" t="n">
+        <v>284.51</v>
+      </c>
+      <c r="E350" t="n">
+        <v>294.66</v>
+      </c>
+      <c r="F350" t="n">
+        <v>300.05</v>
+      </c>
+      <c r="G350" t="n">
+        <v>293.73</v>
+      </c>
+      <c r="H350" t="n">
+        <v>292.42</v>
+      </c>
+      <c r="I350" t="n">
+        <v>296.75</v>
+      </c>
+      <c r="J350" t="n">
+        <v>306.99</v>
+      </c>
+      <c r="K350" t="n">
+        <v>316.92</v>
+      </c>
+      <c r="L350" t="n">
+        <v>321.1</v>
+      </c>
+      <c r="M350" t="n">
+        <v>323.32</v>
+      </c>
+      <c r="N350" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="O350" t="n">
+        <v>327.87</v>
+      </c>
+      <c r="P350" t="n">
+        <v>330.35</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>329.89</v>
+      </c>
+      <c r="R350" t="n">
+        <v>327.44</v>
+      </c>
+      <c r="S350" t="n">
+        <v>328.55</v>
+      </c>
+      <c r="T350" t="n">
+        <v>325.51</v>
+      </c>
+      <c r="U350" t="n">
+        <v>322.87</v>
+      </c>
+      <c r="V350" t="n">
+        <v>325.95</v>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26455,7 +26680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B350"/>
+  <dimension ref="A1:B353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29958,6 +30183,36 @@
       </c>
       <c r="B350" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -30126,28 +30381,28 @@
         <v>0.035</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4092491751053555</v>
+        <v>0.3963625173356836</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0293813346775833</v>
+        <v>0.02806350790334722</v>
       </c>
       <c r="M2" t="n">
-        <v>14.68882547009425</v>
+        <v>14.63763431812512</v>
       </c>
       <c r="N2" t="n">
-        <v>308.0549190071771</v>
+        <v>305.9669331525759</v>
       </c>
       <c r="O2" t="n">
-        <v>17.55149335547198</v>
+        <v>17.49191050607611</v>
       </c>
       <c r="P2" t="n">
-        <v>281.9761285128829</v>
+        <v>282.1148561677154</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30204,28 +30459,28 @@
         <v>0.0704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3414550015946736</v>
+        <v>0.3148550978668461</v>
       </c>
       <c r="J3" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04486014665442595</v>
+        <v>0.03851090216539521</v>
       </c>
       <c r="M3" t="n">
-        <v>9.185444812611616</v>
+        <v>9.24008012604062</v>
       </c>
       <c r="N3" t="n">
-        <v>137.01802189407</v>
+        <v>137.9853839651418</v>
       </c>
       <c r="O3" t="n">
-        <v>11.70546974256352</v>
+        <v>11.74671800824136</v>
       </c>
       <c r="P3" t="n">
-        <v>282.9618074931431</v>
+        <v>283.2496607048953</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30282,28 +30537,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3018305986005643</v>
+        <v>0.2891125183993133</v>
       </c>
       <c r="J4" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K4" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07230064949740511</v>
+        <v>0.06743293458382282</v>
       </c>
       <c r="M4" t="n">
-        <v>6.667909822190339</v>
+        <v>6.670356697915922</v>
       </c>
       <c r="N4" t="n">
-        <v>64.93969767723861</v>
+        <v>64.86336045992347</v>
       </c>
       <c r="O4" t="n">
-        <v>8.058517089219245</v>
+        <v>8.053779265656805</v>
       </c>
       <c r="P4" t="n">
-        <v>284.3762635606916</v>
+        <v>284.5131914574864</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30360,28 +30615,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.264392367464489</v>
+        <v>0.2491653177985505</v>
       </c>
       <c r="J5" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K5" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07673870330343024</v>
+        <v>0.06898985403858926</v>
       </c>
       <c r="M5" t="n">
-        <v>5.671584669950004</v>
+        <v>5.698307142436074</v>
       </c>
       <c r="N5" t="n">
-        <v>46.72256530986801</v>
+        <v>47.01127259905024</v>
       </c>
       <c r="O5" t="n">
-        <v>6.835390647934323</v>
+        <v>6.856476689893304</v>
       </c>
       <c r="P5" t="n">
-        <v>296.4008289078362</v>
+        <v>296.56475545082</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30438,28 +30693,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1973117222012385</v>
+        <v>0.1794958985448258</v>
       </c>
       <c r="J6" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K6" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06056606218791749</v>
+        <v>0.05020070105679053</v>
       </c>
       <c r="M6" t="n">
-        <v>4.73465043600951</v>
+        <v>4.787355012286371</v>
       </c>
       <c r="N6" t="n">
-        <v>33.54759259920504</v>
+        <v>34.20493417849095</v>
       </c>
       <c r="O6" t="n">
-        <v>5.792028366574618</v>
+        <v>5.848498455030227</v>
       </c>
       <c r="P6" t="n">
-        <v>305.3056491930851</v>
+        <v>305.4974514516437</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30516,28 +30771,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.140917325783789</v>
+        <v>0.1256759428104328</v>
       </c>
       <c r="J7" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K7" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03271018963730621</v>
+        <v>0.02612271635584118</v>
       </c>
       <c r="M7" t="n">
-        <v>4.589819184110389</v>
+        <v>4.631917245778136</v>
       </c>
       <c r="N7" t="n">
-        <v>32.95147651628875</v>
+        <v>33.37148894981912</v>
       </c>
       <c r="O7" t="n">
-        <v>5.740337665703016</v>
+        <v>5.776806120151439</v>
       </c>
       <c r="P7" t="n">
-        <v>298.7690441872758</v>
+        <v>298.9319733349029</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30594,28 +30849,28 @@
         <v>0.1817</v>
       </c>
       <c r="I8" t="n">
-        <v>0.139937036889438</v>
+        <v>0.1266253556307013</v>
       </c>
       <c r="J8" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K8" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03923194599467039</v>
+        <v>0.03231555808975883</v>
       </c>
       <c r="M8" t="n">
-        <v>4.116116536471838</v>
+        <v>4.150515003371984</v>
       </c>
       <c r="N8" t="n">
-        <v>26.64174881590479</v>
+        <v>26.94145781150216</v>
       </c>
       <c r="O8" t="n">
-        <v>5.161564570544942</v>
+        <v>5.190516141146482</v>
       </c>
       <c r="P8" t="n">
-        <v>296.3059345129201</v>
+        <v>296.4492368247924</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30672,28 +30927,28 @@
         <v>0.181</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1773899604986671</v>
+        <v>0.1632385903199036</v>
       </c>
       <c r="J9" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K9" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05010199180183694</v>
+        <v>0.04277853056164405</v>
       </c>
       <c r="M9" t="n">
-        <v>4.7036584800029</v>
+        <v>4.740728758228687</v>
       </c>
       <c r="N9" t="n">
-        <v>33.14352819388954</v>
+        <v>33.45722193586466</v>
       </c>
       <c r="O9" t="n">
-        <v>5.757041618217602</v>
+        <v>5.784221809013262</v>
       </c>
       <c r="P9" t="n">
-        <v>299.8026993923205</v>
+        <v>299.9550379640144</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30750,28 +31005,28 @@
         <v>0.1413</v>
       </c>
       <c r="I10" t="n">
-        <v>0.114756420549952</v>
+        <v>0.1011874093891495</v>
       </c>
       <c r="J10" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K10" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02520968495242581</v>
+        <v>0.01969432412946159</v>
       </c>
       <c r="M10" t="n">
-        <v>4.354795456333021</v>
+        <v>4.380957891020529</v>
       </c>
       <c r="N10" t="n">
-        <v>28.28892554960526</v>
+        <v>28.59769485839917</v>
       </c>
       <c r="O10" t="n">
-        <v>5.318733453521173</v>
+        <v>5.347681259985412</v>
       </c>
       <c r="P10" t="n">
-        <v>311.4417513636312</v>
+        <v>311.5878177081648</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30828,28 +31083,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07063726569145931</v>
+        <v>0.06218864801573593</v>
       </c>
       <c r="J11" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K11" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01090294023309868</v>
+        <v>0.008558151105765743</v>
       </c>
       <c r="M11" t="n">
-        <v>4.093744383738148</v>
+        <v>4.106233234357006</v>
       </c>
       <c r="N11" t="n">
-        <v>24.89715226123369</v>
+        <v>24.89207383676782</v>
       </c>
       <c r="O11" t="n">
-        <v>4.989704626652132</v>
+        <v>4.989195710409426</v>
       </c>
       <c r="P11" t="n">
-        <v>319.8106189144109</v>
+        <v>319.9022017016641</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30906,28 +31161,28 @@
         <v>0.1257</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1523799752370807</v>
+        <v>0.1456797939385518</v>
       </c>
       <c r="J12" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K12" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06335862116086133</v>
+        <v>0.05886420786901558</v>
       </c>
       <c r="M12" t="n">
-        <v>3.44117354324751</v>
+        <v>3.450088606670719</v>
       </c>
       <c r="N12" t="n">
-        <v>18.88035067500604</v>
+        <v>18.85172850982421</v>
       </c>
       <c r="O12" t="n">
-        <v>4.345152549106421</v>
+        <v>4.341857725654332</v>
       </c>
       <c r="P12" t="n">
-        <v>320.812671853492</v>
+        <v>320.8852958472457</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30984,28 +31239,28 @@
         <v>0.1818</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09158922829311845</v>
+        <v>0.08408333607890238</v>
       </c>
       <c r="J13" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K13" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01840672699047863</v>
+        <v>0.01573629112952457</v>
       </c>
       <c r="M13" t="n">
-        <v>3.707221335967861</v>
+        <v>3.712520789778313</v>
       </c>
       <c r="N13" t="n">
-        <v>25.10246354405853</v>
+        <v>25.06191997002351</v>
       </c>
       <c r="O13" t="n">
-        <v>5.010235877087877</v>
+        <v>5.006188167660452</v>
       </c>
       <c r="P13" t="n">
-        <v>324.9493638290996</v>
+        <v>325.0295892678192</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31062,28 +31317,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1270402144106257</v>
+        <v>0.1192663214057069</v>
       </c>
       <c r="J14" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K14" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03098752849172648</v>
+        <v>0.02773443743609971</v>
       </c>
       <c r="M14" t="n">
-        <v>4.221647436497892</v>
+        <v>4.227445231732032</v>
       </c>
       <c r="N14" t="n">
-        <v>28.32027110921801</v>
+        <v>28.26093786720867</v>
       </c>
       <c r="O14" t="n">
-        <v>5.321679350469926</v>
+        <v>5.316101754783167</v>
       </c>
       <c r="P14" t="n">
-        <v>328.4537198237601</v>
+        <v>328.5368167240326</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31140,28 +31395,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1174928219965898</v>
+        <v>0.1117150754276367</v>
       </c>
       <c r="J15" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K15" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02222344632234452</v>
+        <v>0.02044394654547932</v>
       </c>
       <c r="M15" t="n">
-        <v>4.820361290532832</v>
+        <v>4.807087699920523</v>
       </c>
       <c r="N15" t="n">
-        <v>34.0818706203598</v>
+        <v>33.89015082288053</v>
       </c>
       <c r="O15" t="n">
-        <v>5.837968021525966</v>
+        <v>5.821524785043909</v>
       </c>
       <c r="P15" t="n">
-        <v>327.9746646636634</v>
+        <v>328.0364265769445</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31218,28 +31473,28 @@
         <v>0.1317</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05959084320483628</v>
+        <v>0.05975099337563254</v>
       </c>
       <c r="J16" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K16" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L16" t="n">
-        <v>0.006057117490805175</v>
+        <v>0.006203775045915405</v>
       </c>
       <c r="M16" t="n">
-        <v>4.664279183392305</v>
+        <v>4.626467128587685</v>
       </c>
       <c r="N16" t="n">
-        <v>32.05096634134929</v>
+        <v>31.77482114046642</v>
       </c>
       <c r="O16" t="n">
-        <v>5.661357287908023</v>
+        <v>5.636915924551866</v>
       </c>
       <c r="P16" t="n">
-        <v>329.0516235498417</v>
+        <v>329.0498899011156</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31296,28 +31551,28 @@
         <v>0.1248</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1036541280682289</v>
+        <v>0.09880893824121875</v>
       </c>
       <c r="J17" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K17" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01221483699880077</v>
+        <v>0.01130266676335379</v>
       </c>
       <c r="M17" t="n">
-        <v>5.732753091008317</v>
+        <v>5.705089261822233</v>
       </c>
       <c r="N17" t="n">
-        <v>47.78973964496726</v>
+        <v>47.44893379273095</v>
       </c>
       <c r="O17" t="n">
-        <v>6.913012342312666</v>
+        <v>6.888318647734797</v>
       </c>
       <c r="P17" t="n">
-        <v>330.7572789568126</v>
+        <v>330.8098167709585</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31374,28 +31629,28 @@
         <v>0.1538</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1106076599399132</v>
+        <v>0.106342067103409</v>
       </c>
       <c r="J18" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K18" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01580077181715767</v>
+        <v>0.01487493575607923</v>
       </c>
       <c r="M18" t="n">
-        <v>5.326294438219753</v>
+        <v>5.300542443245724</v>
       </c>
       <c r="N18" t="n">
-        <v>41.91425620864013</v>
+        <v>41.61002911415168</v>
       </c>
       <c r="O18" t="n">
-        <v>6.474122041531201</v>
+        <v>6.450583625855236</v>
       </c>
       <c r="P18" t="n">
-        <v>327.8559308761523</v>
+        <v>327.9021881860482</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31452,28 +31707,28 @@
         <v>0.1598</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1500029071758751</v>
+        <v>0.1505978421553464</v>
       </c>
       <c r="J19" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K19" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0201197730327427</v>
+        <v>0.02064409250079713</v>
       </c>
       <c r="M19" t="n">
-        <v>6.502583737801496</v>
+        <v>6.45725778103168</v>
       </c>
       <c r="N19" t="n">
-        <v>60.8790613419981</v>
+        <v>60.37260100557767</v>
       </c>
       <c r="O19" t="n">
-        <v>7.802503530406001</v>
+        <v>7.769980759665861</v>
       </c>
       <c r="P19" t="n">
-        <v>325.8692582879608</v>
+        <v>325.8628835379014</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31530,28 +31785,28 @@
         <v>0.1221</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09671264731669751</v>
+        <v>0.09211694303224717</v>
       </c>
       <c r="J20" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K20" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00893046475662973</v>
+        <v>0.00824575825521412</v>
       </c>
       <c r="M20" t="n">
-        <v>6.466583470965025</v>
+        <v>6.433573634475866</v>
       </c>
       <c r="N20" t="n">
-        <v>57.66539708260522</v>
+        <v>57.26775262074401</v>
       </c>
       <c r="O20" t="n">
-        <v>7.593773573303672</v>
+        <v>7.567546010480809</v>
       </c>
       <c r="P20" t="n">
-        <v>327.7911207687069</v>
+        <v>327.8406412734277</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31608,28 +31863,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1794449472066879</v>
+        <v>0.1726344300021803</v>
       </c>
       <c r="J21" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K21" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02067643877168834</v>
+        <v>0.01947998429952558</v>
       </c>
       <c r="M21" t="n">
-        <v>7.662045882713426</v>
+        <v>7.628943458569718</v>
       </c>
       <c r="N21" t="n">
-        <v>84.72890817828319</v>
+        <v>84.17445805498737</v>
       </c>
       <c r="O21" t="n">
-        <v>9.204830697969582</v>
+        <v>9.174663920547028</v>
       </c>
       <c r="P21" t="n">
-        <v>323.9816476439843</v>
+        <v>324.055012282914</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31686,28 +31941,28 @@
         <v>0.1552</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1376520282747651</v>
+        <v>0.1288076415761191</v>
       </c>
       <c r="J22" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K22" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01592636532723724</v>
+        <v>0.01417836377496595</v>
       </c>
       <c r="M22" t="n">
-        <v>6.607255160811632</v>
+        <v>6.590999502333783</v>
       </c>
       <c r="N22" t="n">
-        <v>65.43223530226518</v>
+        <v>65.11089162673224</v>
       </c>
       <c r="O22" t="n">
-        <v>8.089019427734438</v>
+        <v>8.069132024371161</v>
       </c>
       <c r="P22" t="n">
-        <v>328.3401918077697</v>
+        <v>328.4353119738447</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31745,7 +32000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W347"/>
+  <dimension ref="A1:W350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72239,6 +72494,357 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-36.70691186624136,175.60887532185276</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-36.707547847488875,175.6093121797168</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-36.70810762327213,175.60987887700765</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-36.708650147989395,175.6104749606476</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-36.70922115731755,175.61105832336767</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-36.709846398480465,175.61158193386711</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-36.71040716144082,175.61217178874034</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-36.710925843419076,175.61279527134272</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-36.71141737522864,175.6134818512399</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-36.71188200542231,175.61422197506994</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-36.712336525003,175.61494546963556</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-36.71279664842756,175.6156411381875</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>-36.713230942088174,175.61637808584203</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>-36.71365317182582,175.6171210548918</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>-36.71405071201165,175.61787015131543</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>-36.71447437275185,175.61861416513662</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>-36.71486595202471,175.619387025193</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>-36.7152092144422,175.62017778474876</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>-36.715590154658955,175.62095295353438</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>-36.715941581170355,175.6217509942575</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>-36.716257477932025,175.6225589979548</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-36.70692810399359,175.60884765423125</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-36.707570028553874,175.60927438516094</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-36.70811149702113,175.60987227649937</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-36.70864951120492,175.61047604566625</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-36.709224089596766,175.61105364325917</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-36.70984527716422,175.61158354009612</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-36.71040298907479,175.61217751163142</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-36.710921852441466,175.61280074542458</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-36.71140952040809,175.61349202909062</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-36.711879334035515,175.61422497894205</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-36.71232731081059,175.61495498250812</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-36.712785065183596,175.61565288659344</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>-36.71322538894861,175.61638324924496</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>-36.71365162027122,175.6171223994134</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>-36.71404797831116,175.61787252022745</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>-36.71447985351608,175.61860985638538</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>-36.714874020669,175.61938133351143</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>-36.715223495083734,175.62016777898342</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>-36.71561753165665,175.6209351555601</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>-36.71597396984539,175.6217316309733</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>-36.71627852425275,175.62254648596098</t>
+        </is>
+      </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-36.70695092173978,175.6088087748738</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-36.70758233957077,175.6092534082687</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-36.70811261138723,175.60987037772293</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-36.708647866178296,175.61047884863098</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-36.70922204253393,175.61105691050477</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-36.709842798465125,175.61158709070742</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-36.71040238438405,175.61217834103584</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-36.71091816381044,175.61280580480278</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-36.711408211271255,175.61349372539883</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-36.71187859940412,175.61422580500684</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-36.712330220555636,175.61495197844334</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>-36.71278639097663,175.61565154189654</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>-36.71322481199904,175.6163837857024</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>-36.713649994833055,175.6171238079598</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>-36.71405374124728,175.6178675263046</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>-36.7144860954974,175.61860494919574</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>-36.71488013090433,175.6193770233052</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>-36.71523636335349,175.62015876279614</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>-36.715629504103894,175.62092737218555</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>-36.715980544989634,175.6217277000791</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>-36.716277874173365,175.62254687243194</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0154/nzd0154.xlsx
+++ b/data/nzd0154/nzd0154.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W350"/>
+  <dimension ref="A1:W351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26664,6 +26664,81 @@
         <v>325.95</v>
       </c>
       <c r="W350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>282.31</v>
+      </c>
+      <c r="C351" t="n">
+        <v>273.87</v>
+      </c>
+      <c r="D351" t="n">
+        <v>283.94</v>
+      </c>
+      <c r="E351" t="n">
+        <v>294.88</v>
+      </c>
+      <c r="F351" t="n">
+        <v>300.35</v>
+      </c>
+      <c r="G351" t="n">
+        <v>294.06</v>
+      </c>
+      <c r="H351" t="n">
+        <v>292.71</v>
+      </c>
+      <c r="I351" t="n">
+        <v>297.12</v>
+      </c>
+      <c r="J351" t="n">
+        <v>307.15</v>
+      </c>
+      <c r="K351" t="n">
+        <v>317</v>
+      </c>
+      <c r="L351" t="n">
+        <v>321.13</v>
+      </c>
+      <c r="M351" t="n">
+        <v>323.32</v>
+      </c>
+      <c r="N351" t="n">
+        <v>327.44</v>
+      </c>
+      <c r="O351" t="n">
+        <v>327.76</v>
+      </c>
+      <c r="P351" t="n">
+        <v>329.58</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>329.44</v>
+      </c>
+      <c r="R351" t="n">
+        <v>326.58</v>
+      </c>
+      <c r="S351" t="n">
+        <v>327.54</v>
+      </c>
+      <c r="T351" t="n">
+        <v>324.32</v>
+      </c>
+      <c r="U351" t="n">
+        <v>322.27</v>
+      </c>
+      <c r="V351" t="n">
+        <v>329.56</v>
+      </c>
+      <c r="W351" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26680,7 +26755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30213,6 +30288,16 @@
       </c>
       <c r="B353" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>-0.64</v>
       </c>
     </row>
   </sheetData>
@@ -30381,28 +30466,28 @@
         <v>0.035</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3963625173356836</v>
+        <v>0.3905250189848118</v>
       </c>
       <c r="J2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02806350790334722</v>
+        <v>0.02740149526384994</v>
       </c>
       <c r="M2" t="n">
-        <v>14.63763431812512</v>
+        <v>14.62968173740889</v>
       </c>
       <c r="N2" t="n">
-        <v>305.9669331525759</v>
+        <v>305.3997084800716</v>
       </c>
       <c r="O2" t="n">
-        <v>17.49191050607611</v>
+        <v>17.47568907025046</v>
       </c>
       <c r="P2" t="n">
-        <v>282.1148561677154</v>
+        <v>282.1778696335095</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30459,28 +30544,28 @@
         <v>0.0704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3148550978668461</v>
+        <v>0.3048412533181628</v>
       </c>
       <c r="J3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K3" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03851090216539521</v>
+        <v>0.03617328438363565</v>
       </c>
       <c r="M3" t="n">
-        <v>9.24008012604062</v>
+        <v>9.264076806667061</v>
       </c>
       <c r="N3" t="n">
-        <v>137.9853839651418</v>
+        <v>138.495919166939</v>
       </c>
       <c r="O3" t="n">
-        <v>11.74671800824136</v>
+        <v>11.76842891667953</v>
       </c>
       <c r="P3" t="n">
-        <v>283.2496607048953</v>
+        <v>283.3583463790254</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30537,28 +30622,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2891125183993133</v>
+        <v>0.2844535552492758</v>
       </c>
       <c r="J4" t="n">
+        <v>350</v>
+      </c>
+      <c r="K4" t="n">
         <v>349</v>
       </c>
-      <c r="K4" t="n">
-        <v>348</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.06743293458382282</v>
+        <v>0.06560752154902916</v>
       </c>
       <c r="M4" t="n">
-        <v>6.670356697915922</v>
+        <v>6.673446951330925</v>
       </c>
       <c r="N4" t="n">
-        <v>64.86336045992347</v>
+        <v>64.87556404927568</v>
       </c>
       <c r="O4" t="n">
-        <v>8.053779265656805</v>
+        <v>8.054536861252526</v>
       </c>
       <c r="P4" t="n">
-        <v>284.5131914574864</v>
+        <v>284.5635075042729</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30615,28 +30700,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2491653177985505</v>
+        <v>0.244485028205283</v>
       </c>
       <c r="J5" t="n">
+        <v>350</v>
+      </c>
+      <c r="K5" t="n">
         <v>349</v>
       </c>
-      <c r="K5" t="n">
-        <v>348</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.06898985403858926</v>
+        <v>0.06671132696992532</v>
       </c>
       <c r="M5" t="n">
-        <v>5.698307142436074</v>
+        <v>5.705918517628586</v>
       </c>
       <c r="N5" t="n">
-        <v>47.01127259905024</v>
+        <v>47.07644568148238</v>
       </c>
       <c r="O5" t="n">
-        <v>6.856476689893304</v>
+        <v>6.861227709490655</v>
       </c>
       <c r="P5" t="n">
-        <v>296.56475545082</v>
+        <v>296.6153018197363</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30693,28 +30778,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1794958985448258</v>
+        <v>0.1739298967847511</v>
       </c>
       <c r="J6" t="n">
+        <v>350</v>
+      </c>
+      <c r="K6" t="n">
         <v>349</v>
       </c>
-      <c r="K6" t="n">
-        <v>348</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.05020070105679053</v>
+        <v>0.04718588678595925</v>
       </c>
       <c r="M6" t="n">
-        <v>4.787355012286371</v>
+        <v>4.804388504172066</v>
       </c>
       <c r="N6" t="n">
-        <v>34.20493417849095</v>
+        <v>34.38961000825126</v>
       </c>
       <c r="O6" t="n">
-        <v>5.848498455030227</v>
+        <v>5.864265513109998</v>
       </c>
       <c r="P6" t="n">
-        <v>305.4974514516437</v>
+        <v>305.5575633683845</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30771,28 +30856,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1256759428104328</v>
+        <v>0.1211114794374753</v>
       </c>
       <c r="J7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02612271635584118</v>
+        <v>0.02431308060703052</v>
       </c>
       <c r="M7" t="n">
-        <v>4.631917245778136</v>
+        <v>4.64296502716592</v>
       </c>
       <c r="N7" t="n">
-        <v>33.37148894981912</v>
+        <v>33.46902319782212</v>
       </c>
       <c r="O7" t="n">
-        <v>5.776806120151439</v>
+        <v>5.785241844367625</v>
       </c>
       <c r="P7" t="n">
-        <v>298.9319733349029</v>
+        <v>298.9809246021682</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30849,28 +30934,28 @@
         <v>0.1817</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1266253556307013</v>
+        <v>0.1226377910344664</v>
       </c>
       <c r="J8" t="n">
+        <v>350</v>
+      </c>
+      <c r="K8" t="n">
         <v>349</v>
       </c>
-      <c r="K8" t="n">
-        <v>348</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.03231555808975883</v>
+        <v>0.03039567375310126</v>
       </c>
       <c r="M8" t="n">
-        <v>4.150515003371984</v>
+        <v>4.159699579146442</v>
       </c>
       <c r="N8" t="n">
-        <v>26.94145781150216</v>
+        <v>27.00934928396149</v>
       </c>
       <c r="O8" t="n">
-        <v>5.190516141146482</v>
+        <v>5.197051980109636</v>
       </c>
       <c r="P8" t="n">
-        <v>296.4492368247924</v>
+        <v>296.4923018760339</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30927,28 +31012,28 @@
         <v>0.181</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1632385903199036</v>
+        <v>0.1592071926483322</v>
       </c>
       <c r="J9" t="n">
+        <v>350</v>
+      </c>
+      <c r="K9" t="n">
         <v>349</v>
       </c>
-      <c r="K9" t="n">
-        <v>348</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.04277853056164405</v>
+        <v>0.04084392408629844</v>
       </c>
       <c r="M9" t="n">
-        <v>4.740728758228687</v>
+        <v>4.749054828768503</v>
       </c>
       <c r="N9" t="n">
-        <v>33.45722193586466</v>
+        <v>33.50965086341295</v>
       </c>
       <c r="O9" t="n">
-        <v>5.784221809013262</v>
+        <v>5.788752098977201</v>
       </c>
       <c r="P9" t="n">
-        <v>299.9550379640144</v>
+        <v>299.998576405364</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31005,28 +31090,28 @@
         <v>0.1413</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1011874093891495</v>
+        <v>0.09719181980458927</v>
       </c>
       <c r="J10" t="n">
+        <v>350</v>
+      </c>
+      <c r="K10" t="n">
         <v>349</v>
       </c>
-      <c r="K10" t="n">
-        <v>348</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.01969432412946159</v>
+        <v>0.01821630020658016</v>
       </c>
       <c r="M10" t="n">
-        <v>4.380957891020529</v>
+        <v>4.387156477267755</v>
       </c>
       <c r="N10" t="n">
-        <v>28.59769485839917</v>
+        <v>28.66142523235528</v>
       </c>
       <c r="O10" t="n">
-        <v>5.347681259985412</v>
+        <v>5.353636636189953</v>
       </c>
       <c r="P10" t="n">
-        <v>311.5878177081648</v>
+        <v>311.6309694279792</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31083,28 +31168,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06218864801573593</v>
+        <v>0.05961668352767369</v>
       </c>
       <c r="J11" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K11" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L11" t="n">
-        <v>0.008558151105765743</v>
+        <v>0.007899963943805655</v>
       </c>
       <c r="M11" t="n">
-        <v>4.106233234357006</v>
+        <v>4.108881588883514</v>
       </c>
       <c r="N11" t="n">
-        <v>24.89207383676782</v>
+        <v>24.88004050744859</v>
       </c>
       <c r="O11" t="n">
-        <v>4.989195710409426</v>
+        <v>4.987989625836104</v>
       </c>
       <c r="P11" t="n">
-        <v>319.9022017016641</v>
+        <v>319.9301708034204</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31161,28 +31246,28 @@
         <v>0.1257</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1456797939385518</v>
+        <v>0.1436155266602134</v>
       </c>
       <c r="J12" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K12" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05886420786901558</v>
+        <v>0.05752688952752483</v>
       </c>
       <c r="M12" t="n">
-        <v>3.450088606670719</v>
+        <v>3.451977553084017</v>
       </c>
       <c r="N12" t="n">
-        <v>18.85172850982421</v>
+        <v>18.8358822945726</v>
       </c>
       <c r="O12" t="n">
-        <v>4.341857725654332</v>
+        <v>4.340032522294344</v>
       </c>
       <c r="P12" t="n">
-        <v>320.8852958472457</v>
+        <v>320.9077439416218</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31239,28 +31324,28 @@
         <v>0.1818</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08408333607890238</v>
+        <v>0.08188895943184447</v>
       </c>
       <c r="J13" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K13" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01573629112952457</v>
+        <v>0.01500176406867593</v>
       </c>
       <c r="M13" t="n">
-        <v>3.712520789778313</v>
+        <v>3.713154934812454</v>
       </c>
       <c r="N13" t="n">
-        <v>25.06191997002351</v>
+        <v>25.03489377472853</v>
       </c>
       <c r="O13" t="n">
-        <v>5.006188167660452</v>
+        <v>5.003488160746314</v>
       </c>
       <c r="P13" t="n">
-        <v>325.0295892678192</v>
+        <v>325.0531227062443</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31317,28 +31402,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1192663214057069</v>
+        <v>0.1168862580321824</v>
       </c>
       <c r="J14" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K14" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02773443743609971</v>
+        <v>0.02677867200524842</v>
       </c>
       <c r="M14" t="n">
-        <v>4.227445231732032</v>
+        <v>4.228128750988977</v>
       </c>
       <c r="N14" t="n">
-        <v>28.26093786720867</v>
+        <v>28.23263536904696</v>
       </c>
       <c r="O14" t="n">
-        <v>5.316101754783167</v>
+        <v>5.313439128196253</v>
       </c>
       <c r="P14" t="n">
-        <v>328.5368167240326</v>
+        <v>328.5623415467305</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31395,28 +31480,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1117150754276367</v>
+        <v>0.1098979764363839</v>
       </c>
       <c r="J15" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K15" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02044394654547932</v>
+        <v>0.01989888083096913</v>
       </c>
       <c r="M15" t="n">
-        <v>4.807087699920523</v>
+        <v>4.802123405914534</v>
       </c>
       <c r="N15" t="n">
-        <v>33.89015082288053</v>
+        <v>33.82388988774137</v>
       </c>
       <c r="O15" t="n">
-        <v>5.821524785043909</v>
+        <v>5.815830971386752</v>
       </c>
       <c r="P15" t="n">
-        <v>328.0364265769445</v>
+        <v>328.0559139276143</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31473,28 +31558,28 @@
         <v>0.1317</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05975099337563254</v>
+        <v>0.05914357849430447</v>
       </c>
       <c r="J16" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K16" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L16" t="n">
-        <v>0.006203775045915405</v>
+        <v>0.006115855715089547</v>
       </c>
       <c r="M16" t="n">
-        <v>4.626467128587685</v>
+        <v>4.616424050998802</v>
       </c>
       <c r="N16" t="n">
-        <v>31.77482114046642</v>
+        <v>31.68683256153155</v>
       </c>
       <c r="O16" t="n">
-        <v>5.636915924551866</v>
+        <v>5.629105840320605</v>
       </c>
       <c r="P16" t="n">
-        <v>329.0498899011156</v>
+        <v>329.0564952989362</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31551,28 +31636,28 @@
         <v>0.1248</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09880893824121875</v>
+        <v>0.09654274981432456</v>
       </c>
       <c r="J17" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K17" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01130266676335379</v>
+        <v>0.01085139327250895</v>
       </c>
       <c r="M17" t="n">
-        <v>5.705089261822233</v>
+        <v>5.698838682420467</v>
       </c>
       <c r="N17" t="n">
-        <v>47.44893379273095</v>
+        <v>47.35877618827311</v>
       </c>
       <c r="O17" t="n">
-        <v>6.888318647734797</v>
+        <v>6.881771297294986</v>
       </c>
       <c r="P17" t="n">
-        <v>330.8098167709585</v>
+        <v>330.8344606783705</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31629,28 +31714,28 @@
         <v>0.1538</v>
       </c>
       <c r="I18" t="n">
-        <v>0.106342067103409</v>
+        <v>0.1039900761586774</v>
       </c>
       <c r="J18" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K18" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01487493575607923</v>
+        <v>0.01430353441515941</v>
       </c>
       <c r="M18" t="n">
-        <v>5.300542443245724</v>
+        <v>5.296443063059072</v>
       </c>
       <c r="N18" t="n">
-        <v>41.61002911415168</v>
+        <v>41.54021387443019</v>
       </c>
       <c r="O18" t="n">
-        <v>6.450583625855236</v>
+        <v>6.445169809588433</v>
       </c>
       <c r="P18" t="n">
-        <v>327.9021881860482</v>
+        <v>327.9277651620789</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31707,28 +31792,28 @@
         <v>0.1598</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1505978421553464</v>
+        <v>0.149275888028101</v>
       </c>
       <c r="J19" t="n">
+        <v>350</v>
+      </c>
+      <c r="K19" t="n">
         <v>349</v>
       </c>
-      <c r="K19" t="n">
-        <v>348</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.02064409250079713</v>
+        <v>0.02040791242841744</v>
       </c>
       <c r="M19" t="n">
-        <v>6.45725778103168</v>
+        <v>6.445678747496547</v>
       </c>
       <c r="N19" t="n">
-        <v>60.37260100557767</v>
+        <v>60.21555946049084</v>
       </c>
       <c r="O19" t="n">
-        <v>7.769980759665861</v>
+        <v>7.759868520825004</v>
       </c>
       <c r="P19" t="n">
-        <v>325.8628835379014</v>
+        <v>325.8771604281824</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31785,28 +31870,28 @@
         <v>0.1221</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09211694303224717</v>
+        <v>0.08877356458046648</v>
       </c>
       <c r="J20" t="n">
+        <v>350</v>
+      </c>
+      <c r="K20" t="n">
         <v>349</v>
       </c>
-      <c r="K20" t="n">
-        <v>348</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.00824575825521412</v>
+        <v>0.007695836907684828</v>
       </c>
       <c r="M20" t="n">
-        <v>6.433573634475866</v>
+        <v>6.431320803972854</v>
       </c>
       <c r="N20" t="n">
-        <v>57.26775262074401</v>
+        <v>57.2056583087274</v>
       </c>
       <c r="O20" t="n">
-        <v>7.567546010480809</v>
+        <v>7.563442226177668</v>
       </c>
       <c r="P20" t="n">
-        <v>327.8406412734277</v>
+        <v>327.8767492187337</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31863,28 +31948,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1726344300021803</v>
+        <v>0.1690483728306819</v>
       </c>
       <c r="J21" t="n">
+        <v>350</v>
+      </c>
+      <c r="K21" t="n">
         <v>349</v>
       </c>
-      <c r="K21" t="n">
-        <v>348</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.01947998429952558</v>
+        <v>0.01878146938139713</v>
       </c>
       <c r="M21" t="n">
-        <v>7.628943458569718</v>
+        <v>7.624283546615199</v>
       </c>
       <c r="N21" t="n">
-        <v>84.17445805498737</v>
+        <v>84.05061137365961</v>
       </c>
       <c r="O21" t="n">
-        <v>9.174663920547028</v>
+        <v>9.167912050933932</v>
       </c>
       <c r="P21" t="n">
-        <v>324.055012282914</v>
+        <v>324.0937411190541</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31941,28 +32026,28 @@
         <v>0.1552</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1288076415761191</v>
+        <v>0.127501215161482</v>
       </c>
       <c r="J22" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K22" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01417836377496595</v>
+        <v>0.01397714516917703</v>
       </c>
       <c r="M22" t="n">
-        <v>6.590999502333783</v>
+        <v>6.577977353289064</v>
       </c>
       <c r="N22" t="n">
-        <v>65.11089162673224</v>
+        <v>64.9384202703577</v>
       </c>
       <c r="O22" t="n">
-        <v>8.069132024371161</v>
+        <v>8.058437830644205</v>
       </c>
       <c r="P22" t="n">
-        <v>328.4353119738447</v>
+        <v>328.449403887234</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32000,7 +32085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W350"/>
+  <dimension ref="A1:W351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72845,6 +72930,123 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-36.7069460398044,175.60881709324994</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-36.707579951658275,175.609257477063</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-36.70811563609503,175.60986522390078</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-36.708646698740004,175.6104808378317</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-36.70922038275321,175.61105955962267</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-36.709840850915754,175.61158988047328</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-36.71040063078083,175.61218074630867</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-36.71091592644398,175.6128088736057</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-36.71140721383365,175.61349501782416</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-36.71187806512676,175.61422640578124</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-36.7123300127167,175.61495219301943</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-36.71278639097663,175.61565154189654</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>-36.71322524471122,175.6163833833593</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>-36.71365080755214,175.61712310368662</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>-36.71405943029942,175.6178625964057</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>-36.71448952097489,175.6186022562255</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>-36.71488686783031,175.61937227102578</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>-36.715244288324214,175.6201532101428</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>-36.71563900224508,175.62092119737343</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>-36.71598541546676,175.62172478830522</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>-36.71624853933989,175.62256431192705</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
